--- a/15 indicadores restantes UMO -2.xlsx
+++ b/15 indicadores restantes UMO -2.xlsx
@@ -1,47 +1,60 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/juanitaospina/Library/Mobile Documents/com~apple~CloudDocs/University /Año 2 Esic/Aldea global 2/Pagina web UMO/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D88604B2-93EF-1C4B-B3FB-616C675CB618}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="4420" yWindow="660" windowWidth="24980" windowHeight="16620" firstSheet="8" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="POLITICO 1" sheetId="1" r:id="rId5"/>
-    <sheet state="visible" name="POLITICO 2" sheetId="2" r:id="rId6"/>
-    <sheet state="visible" name="POLITICO 3" sheetId="3" r:id="rId7"/>
-    <sheet state="visible" name="SOCIALcultural 1" sheetId="4" r:id="rId8"/>
-    <sheet state="visible" name="Social cultural 2" sheetId="5" r:id="rId9"/>
-    <sheet state="visible" name="social cultural 3" sheetId="6" r:id="rId10"/>
-    <sheet state="visible" name="Tecnológico  Geográfico 1" sheetId="7" r:id="rId11"/>
-    <sheet state="visible" name="Tecnológico  Geográfico 2" sheetId="8" r:id="rId12"/>
-    <sheet state="visible" name="Tecnológico  Geográfico 3" sheetId="9" r:id="rId13"/>
-    <sheet state="visible" name="comercio internacional 1" sheetId="10" r:id="rId14"/>
-    <sheet state="visible" name="comercio internacional 2" sheetId="11" r:id="rId15"/>
-    <sheet state="visible" name="comercio internacional 3" sheetId="12" r:id="rId16"/>
-    <sheet state="visible" name="Inversión Extranjera 1" sheetId="13" r:id="rId17"/>
-    <sheet state="visible" name="Inversión Extranjera 2" sheetId="14" r:id="rId18"/>
-    <sheet state="visible" name="Inversión Extranjera 3" sheetId="15" r:id="rId19"/>
+    <sheet name="POLITICO 1" sheetId="1" r:id="rId1"/>
+    <sheet name="POLITICO 2" sheetId="2" r:id="rId2"/>
+    <sheet name="POLITICO 3" sheetId="3" r:id="rId3"/>
+    <sheet name="SOCIALcultural 1" sheetId="4" r:id="rId4"/>
+    <sheet name="Social cultural 2" sheetId="5" r:id="rId5"/>
+    <sheet name="social cultural 3" sheetId="6" r:id="rId6"/>
+    <sheet name="Tecnológico  Geográfico 1" sheetId="7" r:id="rId7"/>
+    <sheet name="Tecnológico  Geográfico 2" sheetId="8" r:id="rId8"/>
+    <sheet name="Tecnológico  Geográfico 3" sheetId="9" r:id="rId9"/>
+    <sheet name="comercio internacional 1" sheetId="10" r:id="rId10"/>
+    <sheet name="comercio internacional 2" sheetId="11" r:id="rId11"/>
+    <sheet name="comercio internacional 3" sheetId="12" r:id="rId12"/>
+    <sheet name="Inversión Extranjera 1" sheetId="13" r:id="rId13"/>
+    <sheet name="Inversión Extranjera 2" sheetId="14" r:id="rId14"/>
+    <sheet name="Inversión Extranjera 3" sheetId="15" r:id="rId15"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="132">
   <si>
     <t>Certeza Jurídica y Contractual (Convención de Viena - CISG)</t>
   </si>
   <si>
     <r>
       <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
-        <b/>
-        <color theme="1"/>
+        <family val="2"/>
       </rPr>
       <t>¿Que mide este indicador?:</t>
     </r>
     <r>
       <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
-        <color theme="1"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> Este indicador mide el nivel de protección
  legal que tiene una empresa al exportar. Evalúa si el estado aplica la
@@ -80,16 +93,20 @@
   <si>
     <r>
       <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
-        <b/>
-        <color theme="1"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">¿Qué mide este indicador?: </t>
     </r>
     <r>
       <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
-        <color theme="1"/>
+        <family val="2"/>
       </rPr>
       <t>Mide el ahorro económico 
 directo para el comprador final. Determina si el estado
@@ -152,16 +169,20 @@
   <si>
     <r>
       <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
-        <b/>
-        <color theme="1"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">¿Que mide este indicador? </t>
     </r>
     <r>
       <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
-        <color theme="1"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">
 Mide cuánta gente es dueña de su casa. Nos interesa porque un propietario tiene jardín, y quien tiene jardín necesita podadora que es el equipo al que UMO le vende el sillín.
@@ -192,16 +213,20 @@
   <si>
     <r>
       <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
-        <b/>
-        <color theme="1"/>
+        <family val="2"/>
       </rPr>
       <t>¿Que mide este indicador?</t>
     </r>
     <r>
       <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
-        <color theme="1"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> Mide qué tan acostumbrada está la gente a comprar accesorios o repuestos adicionales para sus equipos. Nos interesa porque el sillín de UMO no viene con la podadora, se compra aparte como una mejora.</t>
     </r>
@@ -231,16 +256,20 @@
   <si>
     <r>
       <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
-        <b/>
-        <color theme="1"/>
+        <family val="2"/>
       </rPr>
       <t>¿Que mide este indicador?</t>
     </r>
     <r>
       <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
-        <color theme="1"/>
+        <family val="2"/>
       </rPr>
       <t>Mide qué tanto está creciendo el uso de podadoras eléctricas en cada estado. Nos interesa porque si la gente no tiene podadora eléctrica, no hay mercado para el sillín de UMO.</t>
     </r>
@@ -268,16 +297,20 @@
   <si>
     <r>
       <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
-        <b/>
-        <color theme="1"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">¿Que es ese indicador? </t>
     </r>
     <r>
       <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
-        <color theme="1"/>
+        <family val="2"/>
       </rPr>
       <t>Annual Vehicle Miles of Travel dice cuántas millas recorrieron los vehículos en Missouri y Oklahoma durante un año. Sirve para ver cuál estado tiene más movimiento vial, más circulación y más actividad en carretera. Si un estado tiene más movimiento vial, puede indicar que hay más circulación entre ciudades, más actividad comercial y una red de carreteras más usada. Eso puede facilitar que distribuidores, tiendas de repuestos y dealers reciban inventario, hagan reposición y conecten con clientes en diferentes zonas.
 Pero ojo: no te dice cuántos sillines, repuestos o mercancía se movieron. Tampoco separa si fueron carros particulares, camiones o vehículos comerciales. Por eso es un indicador indirecto.</t>
@@ -287,22 +320,10 @@
     <t>Año</t>
   </si>
   <si>
-    <t xml:space="preserve">Missouri: </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oklahoma: </t>
-  </si>
-  <si>
     <t>https://www.fhwa.dot.gov/policyinformation/statistics/2019/vm2.cfm?utm_</t>
   </si>
   <si>
     <t>https://www.fhwa.dot.gov/policyinformation/statistics/2022/vm2.cfm</t>
-  </si>
-  <si>
-    <t>Los datos de 2020 y 2021 salen de FHWA Highway Statistics VM-2</t>
-  </si>
-  <si>
-    <t>Los datos de 2022 y 2023 salen de la misma tabla VM-2 de FHWA para esos años.</t>
   </si>
   <si>
     <t>El indicador de actividad vial y dinamismo de movilidad comercial muestra una ventaja clara para Missouri frente a Oklahoma. Según la Federal Highway Administration, la tabla mide las millas anuales recorridas por vehículos en cada estado, lo que permite comparar el nivel de movimiento vial con una misma fuente oficial. 
@@ -319,9 +340,6 @@
     <t>Variable</t>
   </si>
   <si>
-    <t>(basado en el dato de granjas con acceso a internet)</t>
-  </si>
-  <si>
     <t>Granjas con acceso a internet</t>
   </si>
   <si>
@@ -381,16 +399,20 @@
   <si>
     <r>
       <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
-        <b/>
-        <color theme="1"/>
+        <family val="2"/>
       </rPr>
       <t>Referencias</t>
     </r>
     <r>
       <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
-        <color theme="1"/>
+        <family val="2"/>
       </rPr>
       <t>: USDA NASS, 2022 Census of Agriculture.
 nass.usda.gov/AgCensus — mismo año, misma metodología para ambos estados.</t>
@@ -417,16 +439,20 @@
   <si>
     <r>
       <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
-        <b/>
-        <color theme="1"/>
+        <family val="2"/>
       </rPr>
       <t>¿Que es este indicador?</t>
     </r>
     <r>
       <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
-        <color theme="1"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> Mide la entrada de maquinaria y partes agrícolas al estado. Indica el nivel de demanda y apertura del mercado a productos del exterior.</t>
     </r>
@@ -438,16 +464,10 @@
     <t>$17.00 B</t>
   </si>
   <si>
-    <t>Missouri: 5.0 / 5</t>
-  </si>
-  <si>
     <t xml:space="preserve">$27.30 B	</t>
   </si>
   <si>
     <t>$18.50 B</t>
-  </si>
-  <si>
-    <t>Oklahoma: 3.69 / 5</t>
   </si>
   <si>
     <t>$24.20 B</t>
@@ -471,16 +491,20 @@
   <si>
     <r>
       <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
-        <b/>
-        <color theme="1"/>
+        <family val="2"/>
       </rPr>
       <t>¿Que es este indicador?</t>
     </r>
     <r>
       <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
-        <color theme="1"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> Mide qué tan integrada está la economía estatal con el comercio exterior. Se calcula como exportaciones de bienes como % del PIB estatal.</t>
     </r>
@@ -492,41 +516,53 @@
     <t>Oklahoma (% PIB)</t>
   </si>
   <si>
-    <t>Oklahoma: 3.37 / 5</t>
-  </si>
-  <si>
     <r>
       <rPr>
+        <u/>
+        <sz val="10"/>
         <color rgb="FF1155CC"/>
-        <u/>
+        <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>https://ustr.gov/map/state-benefits/mo</t>
     </r>
     <r>
       <rPr>
+        <sz val="10"/>
         <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">
 </t>
     </r>
     <r>
       <rPr>
+        <u/>
+        <sz val="10"/>
         <color rgb="FF1155CC"/>
-        <u/>
+        <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>https://ustr.gov/map/state-benefits/ok</t>
     </r>
     <r>
       <rPr>
+        <sz val="10"/>
         <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">
 </t>
     </r>
     <r>
       <rPr>
+        <u/>
+        <sz val="10"/>
         <color rgb="FF1155CC"/>
-        <u/>
+        <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.bea.gov/data/gdp/gdp-state</t>
     </r>
@@ -541,16 +577,20 @@
   <si>
     <r>
       <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
-        <b/>
-        <color theme="1"/>
+        <family val="2"/>
       </rPr>
       <t>¿Que es este indicador?</t>
     </r>
     <r>
       <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
-        <color theme="1"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> Mide el tamaño de la red de venta y posventa de maquinaria agrícola. Indica cuántos distribuidores potenciales existen en cada estado.
 </t>
@@ -592,50 +632,71 @@
   <si>
     <r>
       <rPr>
+        <u/>
+        <sz val="10"/>
         <color rgb="FF1155CC"/>
-        <u/>
+        <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>https://data.census.gov</t>
     </r>
     <r>
       <rPr>
+        <sz val="10"/>
         <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">
 </t>
     </r>
     <r>
       <rPr>
+        <u/>
+        <sz val="10"/>
         <color rgb="FF1155CC"/>
-        <u/>
+        <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>https://ustr.gov/map/state-benefits/mo</t>
     </r>
     <r>
       <rPr>
+        <sz val="10"/>
         <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">
 </t>
     </r>
     <r>
       <rPr>
+        <u/>
+        <sz val="10"/>
         <color rgb="FF1155CC"/>
-        <u/>
+        <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>https://ustr.gov/map/state-benefits/ok</t>
     </r>
     <r>
       <rPr>
+        <sz val="10"/>
         <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">
 </t>
     </r>
     <r>
       <rPr>
+        <u/>
+        <sz val="10"/>
         <color rgb="FF1155CC"/>
-        <u/>
+        <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.nass.usda.gov/AgCensus</t>
     </r>
@@ -650,16 +711,20 @@
   <si>
     <r>
       <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
-        <b/>
-        <color theme="1"/>
+        <family val="2"/>
       </rPr>
       <t>¿Que es este indicador?:</t>
     </r>
     <r>
       <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
-        <color theme="1"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> Mide programas estatales de apoyo a expansión/retención mediante créditos fiscales, retención de withholding tax, reembolsos en efectivo o beneficios vinculados a empleo e inversión.</t>
     </r>
@@ -667,17 +732,21 @@
   <si>
     <r>
       <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
-        <b/>
-        <color theme="1"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">Market Viability Score 
 </t>
     </r>
     <r>
       <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
-        <color theme="1"/>
+        <family val="2"/>
       </rPr>
       <t>Missouri: 5
 Oklahoma: 4.3</t>
@@ -687,26 +756,40 @@
     <r>
       <rPr>
         <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">Referencias:
 </t>
     </r>
     <r>
       <rPr>
+        <u/>
+        <sz val="10"/>
         <color rgb="FF1155CC"/>
-        <u/>
+        <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>https://ded.mo.gov/programs/business/missouri-works</t>
     </r>
     <r>
-      <rPr/>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">
 </t>
     </r>
     <r>
       <rPr>
+        <u/>
+        <sz val="10"/>
         <color rgb="FF1155CC"/>
-        <u/>
+        <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>https://oksenate.gov/sites/default/files/2023-11/Dept.%20of%20Commerce%20Quality%20Jobs%20Briefing%2010.3.2023.pdf</t>
     </r>
@@ -722,16 +805,22 @@
   <si>
     <r>
       <rPr>
-        <rFont val="var(--pplx-sans), ui-sans-serif, system-ui, -apple-system, BlinkMacSystemFont, &quot;Segoe UI&quot;, Roboto, Helvetica Neue, Arial, &quot;Noto Sans&quot;, var(--pplx-cjk-sans), sans-serif, &quot;Apple Color Emoji&quot;, &quot;Segoe UI Emoji&quot;, &quot;Segoe UI Symbol&quot;, &quot;Noto Color Emoji&quot;"/>
         <b/>
+        <sz val="10"/>
         <color rgb="FF27251E"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">¿Que es este indicador?: </t>
     </r>
     <r>
       <rPr>
-        <rFont val="var(--pplx-sans), ui-sans-serif, system-ui, -apple-system, BlinkMacSystemFont, &quot;Segoe UI&quot;, Roboto, Helvetica Neue, Arial, &quot;Noto Sans&quot;, var(--pplx-cjk-sans), sans-serif, &quot;Apple Color Emoji&quot;, &quot;Segoe UI Emoji&quot;, &quot;Segoe UI Symbol&quot;, &quot;Noto Color Emoji&quot;"/>
+        <sz val="10"/>
         <color rgb="FF27251E"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>Mide la distribución 
 de proyectos anunciados y/o empleo/capital FDI
@@ -748,26 +837,40 @@
     <r>
       <rPr>
         <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">Referencias: 
 </t>
     </r>
     <r>
       <rPr>
+        <u/>
+        <sz val="10"/>
         <color rgb="FF1155CC"/>
-        <u/>
+        <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.trade.gov/sites/default/files/2023-09/Missouri.pdf</t>
     </r>
     <r>
-      <rPr/>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">
 </t>
     </r>
     <r>
       <rPr>
+        <u/>
+        <sz val="10"/>
         <color rgb="FF1155CC"/>
-        <u/>
+        <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>https://digitalprairie.ok.gov/digital/api/collection/stgovpub/id/731411/download
 https://www.trade.gov/sites/default/files/2023-09/Oklahoma.pdf</t>
@@ -785,16 +888,22 @@
   <si>
     <r>
       <rPr>
-        <rFont val="var(--pplx-sans), ui-sans-serif, system-ui, -apple-system, BlinkMacSystemFont, &quot;Segoe UI&quot;, Roboto, Helvetica Neue, Arial, &quot;Noto Sans&quot;, var(--pplx-cjk-sans), sans-serif, &quot;Apple Color Emoji&quot;, &quot;Segoe UI Emoji&quot;, &quot;Segoe UI Symbol&quot;, &quot;Noto Color Emoji&quot;"/>
         <b/>
+        <sz val="10"/>
         <color rgb="FF27251E"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>¿Que es este indicador?:</t>
     </r>
     <r>
       <rPr>
-        <rFont val="var(--pplx-sans), ui-sans-serif, system-ui, -apple-system, BlinkMacSystemFont, &quot;Segoe UI&quot;, Roboto, Helvetica Neue, Arial, &quot;Noto Sans&quot;, var(--pplx-cjk-sans), sans-serif, &quot;Apple Color Emoji&quot;, &quot;Segoe UI Emoji&quot;, &quot;Segoe UI Symbol&quot;, &quot;Noto Color Emoji&quot;"/>
+        <sz val="10"/>
         <color rgb="FF27251E"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
 Mide el valor de la posición/inversión extranjera directa por industria,
@@ -805,17 +914,21 @@
   <si>
     <r>
       <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
-        <b/>
-        <color theme="1"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">Market Viability Score 
 </t>
     </r>
     <r>
       <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
-        <color theme="1"/>
+        <family val="2"/>
       </rPr>
       <t>Missouri: 5
 Oklahoma: 4.1</t>
@@ -830,32 +943,51 @@
   <si>
     <r>
       <rPr>
+        <u/>
+        <sz val="10"/>
         <color rgb="FF1155CC"/>
-        <u/>
+        <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.bea.gov/data/intl-trade-investment/direct-investment-country-and-industry</t>
     </r>
     <r>
-      <rPr/>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">
 </t>
     </r>
     <r>
       <rPr>
+        <u/>
+        <sz val="10"/>
         <color rgb="FF1155CC"/>
-        <u/>
+        <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.trade.gov/sites/default/files/2023-09/Missouri.pdf</t>
     </r>
     <r>
-      <rPr/>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">
 </t>
     </r>
     <r>
       <rPr>
+        <u/>
+        <sz val="10"/>
         <color rgb="FF1155CC"/>
-        <u/>
+        <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>https://digitalprairie.ok.gov/digital/api/collection/stgovpub/id/731411/download</t>
     </r>
@@ -873,118 +1005,201 @@
 Reto: El volumen total de empleo FDI es inferior al de Missouri (64,700 vs 134,300), sugiriendo un mercado más reducido en términos absolutos.
 Es la opción más atractiva para instalarse o realizar ensamble local, ya que la alta densidad manufacturera ofrece un entorno de operación más directo. </t>
   </si>
+  <si>
+    <t>Oklahoma: 2,83</t>
+  </si>
+  <si>
+    <t>Oklahoma: 3.69</t>
+  </si>
+  <si>
+    <t>Oklahoma: 3.37</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="27">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <u/>
+      <sz val="10"/>
       <color rgb="FF1155CC"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <u/>
+      <sz val="10"/>
       <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
+      <sz val="10"/>
       <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
-      <sz val="9.0"/>
+      <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="&quot;Arial&quot;"/>
     </font>
     <font>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
+      <sz val="10"/>
       <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Var(--pplx-answer)"/>
     </font>
     <font>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Var(--pplx-answer)"/>
     </font>
     <font>
       <u/>
+      <sz val="10"/>
       <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
+      <sz val="10"/>
       <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
-      <sz val="18.0"/>
+      <sz val="18"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color rgb="FF27251E"/>
       <name val="Var(--pplx-sans)"/>
     </font>
     <font>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Var(--pplx-sans)"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF27251E"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF27251E"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="5">
@@ -992,7 +1207,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1014,7 +1229,13 @@
     </fill>
   </fills>
   <borders count="9">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
@@ -1028,27 +1249,34 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color rgb="FF1A3557"/>
       </left>
+      <right/>
       <top style="thin">
         <color rgb="FF1A3557"/>
       </top>
       <bottom style="thin">
         <color rgb="FF1A3557"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color rgb="FF1A3557"/>
       </top>
       <bottom style="thin">
         <color rgb="FF1A3557"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="thin">
         <color rgb="FF1A3557"/>
       </right>
@@ -1058,6 +1286,7 @@
       <bottom style="thin">
         <color rgb="FF1A3557"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -1069,237 +1298,222 @@
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="58">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="2" fontId="9" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    <xf numFmtId="2" fontId="10" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="9" numFmtId="2" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" vertical="center"/>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="10" numFmtId="2" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" vertical="center"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" vertical="center"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="2" fillId="3" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="3" fillId="3" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="0"/>
+    <xf numFmtId="10" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="4" fillId="3" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="3" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="18" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="18" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="9" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="9" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="10" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="5" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="5" fillId="0" fontId="2" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="6" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="6" fillId="0" fontId="2" numFmtId="9" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="6" fillId="0" fontId="2" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="6" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="10" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="5" fillId="0" fontId="2" numFmtId="10" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="top"/>
-    </xf>
-    <xf borderId="7" fillId="4" fontId="19" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="4" fontId="20" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="8" fillId="4" fontId="19" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="2">
     <dxf>
-      <font/>
       <fill>
-        <patternFill patternType="none"/>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF6F8F9"/>
+          <bgColor rgb="FFF6F8F9"/>
+        </patternFill>
       </fill>
-      <border/>
     </dxf>
     <dxf>
-      <font/>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFFFFFFF"/>
           <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
-      <border/>
-    </dxf>
-    <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF6F8F9"/>
-          <bgColor rgb="FFF6F8F9"/>
-        </patternFill>
-      </fill>
-      <border/>
     </dxf>
   </dxfs>
   <tableStyles count="1">
-    <tableStyle count="2" pivot="0" name="SOCIALcultural 1-style">
-      <tableStyleElement dxfId="1" type="firstRowStripe"/>
-      <tableStyleElement dxfId="2" type="secondRowStripe"/>
+    <tableStyle name="SOCIALcultural 1-style" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="secondRowStripe" dxfId="0"/>
     </tableStyle>
   </tableStyles>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="1"/>
+  <c:style val="2"/>
   <c:chart>
     <c:title>
       <c:tx>
@@ -1329,15 +1543,24 @@
       </c:tx>
       <c:overlay val="0"/>
     </c:title>
+    <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
       <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="1"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
               <c:f>'POLITICO 3'!$B$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Missouri</c:v>
+                </c:pt>
+              </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
@@ -1351,17 +1574,53 @@
             <c:symbol val="none"/>
           </c:marker>
           <c:cat>
-            <c:strRef>
+            <c:numRef>
               <c:f>'POLITICO 3'!$A$5:$A$8</c:f>
-            </c:strRef>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2024</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
               <c:f>'POLITICO 3'!$B$5:$B$8</c:f>
-              <c:numCache/>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>92.012</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>90.991</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>91.103999999999999</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>90.816999999999993</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-FCE6-7F4B-9B3E-7A4FF8F20CF0}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="1"/>
@@ -1369,6 +1628,12 @@
           <c:tx>
             <c:strRef>
               <c:f>'POLITICO 3'!$C$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Oklahoma</c:v>
+                </c:pt>
+              </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
@@ -1382,18 +1647,63 @@
             <c:symbol val="none"/>
           </c:marker>
           <c:cat>
-            <c:strRef>
+            <c:numRef>
               <c:f>'POLITICO 3'!$A$5:$A$8</c:f>
-            </c:strRef>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2024</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
               <c:f>'POLITICO 3'!$C$5:$C$8</c:f>
-              <c:numCache/>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>92.4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>91.4</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>91.4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>87.8</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-FCE6-7F4B-9B3E-7A4FF8F20CF0}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
         <c:axId val="1646372103"/>
         <c:axId val="1076310602"/>
       </c:lineChart>
@@ -1435,7 +1745,7 @@
               <c:xMode val="edge"/>
               <c:yMode val="edge"/>
               <c:x val="0.11595247395833333"/>
-              <c:y val="0.9203504043126682"/>
+              <c:y val="0.92035040431266824"/>
             </c:manualLayout>
           </c:layout>
           <c:overlay val="0"/>
@@ -1443,7 +1753,7 @@
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
-        <c:spPr/>
+        <c:tickLblPos val="nextTo"/>
         <c:txPr>
           <a:bodyPr/>
           <a:lstStyle/>
@@ -1456,9 +1766,15 @@
                 <a:latin typeface="+mn-lt"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="en-CO"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="1076310602"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="1"/>
       </c:catAx>
       <c:valAx>
         <c:axId val="1076310602"/>
@@ -1483,7 +1799,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr lvl="0">
-                  <a:defRPr b="0" sz="1000">
+                  <a:defRPr sz="1000" b="0">
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
@@ -1491,7 +1807,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr b="0" sz="1000">
+                  <a:rPr sz="1000" b="0">
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
@@ -1506,7 +1822,7 @@
             <c:manualLayout>
               <c:xMode val="edge"/>
               <c:yMode val="edge"/>
-              <c:x val="0.03091666666666667"/>
+              <c:x val="3.0916666666666669E-2"/>
               <c:y val="0.25952380952380955"/>
             </c:manualLayout>
           </c:layout>
@@ -1531,9 +1847,12 @@
                 <a:latin typeface="+mn-lt"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="en-CO"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="1646372103"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>
@@ -1551,16 +1870,28 @@
               <a:latin typeface="+mn-lt"/>
             </a:defRPr>
           </a:pPr>
+          <a:endParaRPr lang="en-CO"/>
         </a:p>
       </c:txPr>
     </c:legend>
     <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="zero"/>
+    <c:showDLblsOverMax val="1"/>
   </c:chart>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
 </c:chartSpace>
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="1"/>
+  <c:style val="2"/>
   <c:chart>
     <c:title>
       <c:tx>
@@ -1577,7 +1908,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr b="0">
+              <a:rPr lang="en-US" b="0">
                 <a:solidFill>
                   <a:srgbClr val="757575"/>
                 </a:solidFill>
@@ -1590,21 +1921,19 @@
       </c:tx>
       <c:overlay val="0"/>
     </c:title>
+    <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
       <c:barChart>
         <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="1"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'SOCIALcultural 1'!$B$4</c:f>
-            </c:strRef>
-          </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:schemeClr val="accent1"/>
+              <a:srgbClr val="4285F4"/>
             </a:solidFill>
             <a:ln cmpd="sng">
               <a:solidFill>
@@ -1612,8 +1941,15 @@
               </a:solidFill>
             </a:ln>
           </c:spPr>
+          <c:invertIfNegative val="1"/>
           <c:dLbls>
-            <c:numFmt formatCode="General" sourceLinked="1"/>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:txPr>
               <a:bodyPr/>
               <a:lstStyle/>
@@ -1621,6 +1957,7 @@
                 <a:pPr lvl="0">
                   <a:defRPr/>
                 </a:pPr>
+                <a:endParaRPr lang="en-CO"/>
               </a:p>
             </c:txPr>
             <c:showLegendKey val="0"/>
@@ -1629,30 +1966,92 @@
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
             <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="0"/>
+              </c:ext>
+            </c:extLst>
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'SOCIALcultural 1'!$A$5:$A$9</c:f>
+              <c:f>'SOCIALcultural 1'!$A$4:$A$9</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>Año </c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2024</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2025</c:v>
+                </c:pt>
+              </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOCIALcultural 1'!$B$5:$B$9</c:f>
-              <c:numCache/>
+              <c:f>'SOCIALcultural 1'!$B$4:$B$9</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0" formatCode="General">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>72.8</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>70.599999999999994</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>68.7</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>70.5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>68.3</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{6F2FDCE9-48DA-4B69-8628-5D25D57E5C99}">
+              <c14:invertSolidFillFmt>
+                <c14:spPr xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF"/>
+                  </a:solidFill>
+                  <a:ln cmpd="sng">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                  </a:ln>
+                </c14:spPr>
+              </c14:invertSolidFillFmt>
+            </c:ext>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-D441-864D-B3BF-703D4EA4C75A}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="1"/>
           <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'SOCIALcultural 1'!$C$4</c:f>
-            </c:strRef>
-          </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:schemeClr val="accent2"/>
+              <a:srgbClr val="EA4335"/>
             </a:solidFill>
             <a:ln cmpd="sng">
               <a:solidFill>
@@ -1660,8 +2059,15 @@
               </a:solidFill>
             </a:ln>
           </c:spPr>
+          <c:invertIfNegative val="1"/>
           <c:dLbls>
-            <c:numFmt formatCode="General" sourceLinked="1"/>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:txPr>
               <a:bodyPr/>
               <a:lstStyle/>
@@ -1669,6 +2075,7 @@
                 <a:pPr lvl="0">
                   <a:defRPr/>
                 </a:pPr>
+                <a:endParaRPr lang="en-CO"/>
               </a:p>
             </c:txPr>
             <c:showLegendKey val="0"/>
@@ -1677,19 +2084,95 @@
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
             <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="0"/>
+              </c:ext>
+            </c:extLst>
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'SOCIALcultural 1'!$A$5:$A$9</c:f>
+              <c:f>'SOCIALcultural 1'!$A$4:$A$9</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>Año </c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2024</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2025</c:v>
+                </c:pt>
+              </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOCIALcultural 1'!$C$5:$C$9</c:f>
-              <c:numCache/>
+              <c:f>'SOCIALcultural 1'!$C$4:$C$9</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0" formatCode="General">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>67</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>68.5</c:v>
+                </c:pt>
+                <c:pt idx="3" formatCode="General">
+                  <c:v>68</c:v>
+                </c:pt>
+                <c:pt idx="4" formatCode="General">
+                  <c:v>66.8</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>63.8</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{6F2FDCE9-48DA-4B69-8628-5D25D57E5C99}">
+              <c14:invertSolidFillFmt>
+                <c14:spPr xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF"/>
+                  </a:solidFill>
+                  <a:ln cmpd="sng">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                  </a:ln>
+                </c14:spPr>
+              </c14:invertSolidFillFmt>
+            </c:ext>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-D441-864D-B3BF-703D4EA4C75A}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
         <c:axId val="1158873644"/>
         <c:axId val="388494629"/>
       </c:barChart>
@@ -1714,15 +2197,7 @@
                     <a:latin typeface="+mn-lt"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:r>
-                  <a:rPr b="0">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                  </a:rPr>
-                  <a:t/>
-                </a:r>
+                <a:endParaRPr lang="en-CO"/>
               </a:p>
             </c:rich>
           </c:tx>
@@ -1731,7 +2206,7 @@
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
-        <c:spPr/>
+        <c:tickLblPos val="nextTo"/>
         <c:txPr>
           <a:bodyPr/>
           <a:lstStyle/>
@@ -1744,9 +2219,15 @@
                 <a:latin typeface="+mn-lt"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="en-CO"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="388494629"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="1"/>
       </c:catAx>
       <c:valAx>
         <c:axId val="388494629"/>
@@ -1789,15 +2270,7 @@
                     <a:latin typeface="+mn-lt"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:r>
-                  <a:rPr b="0">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                  </a:rPr>
-                  <a:t/>
-                </a:r>
+                <a:endParaRPr lang="en-CO"/>
               </a:p>
             </c:rich>
           </c:tx>
@@ -1822,9 +2295,12 @@
                 <a:latin typeface="+mn-lt"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="en-CO"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="1158873644"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>
@@ -1842,16 +2318,28 @@
               <a:latin typeface="+mn-lt"/>
             </a:defRPr>
           </a:pPr>
+          <a:endParaRPr lang="en-CO"/>
         </a:p>
       </c:txPr>
     </c:legend>
     <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="zero"/>
+    <c:showDLblsOverMax val="1"/>
   </c:chart>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
 </c:chartSpace>
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="1"/>
+  <c:style val="2"/>
   <c:chart>
     <c:title>
       <c:tx>
@@ -1860,7 +2348,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr lvl="0">
-              <a:defRPr b="0" sz="1800">
+              <a:defRPr sz="1800" b="0">
                 <a:solidFill>
                   <a:srgbClr val="757575"/>
                 </a:solidFill>
@@ -1868,7 +2356,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr b="0" sz="1800">
+              <a:rPr lang="en-US" sz="1800" b="0">
                 <a:solidFill>
                   <a:srgbClr val="757575"/>
                 </a:solidFill>
@@ -1881,15 +2369,24 @@
       </c:tx>
       <c:overlay val="0"/>
     </c:title>
+    <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
       <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="1"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
               <c:f>'Tecnológico  Geográfico 1'!$B$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Missouri</c:v>
+                </c:pt>
+              </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
@@ -1914,7 +2411,13 @@
             </c:spPr>
           </c:marker>
           <c:dLbls>
-            <c:numFmt formatCode="General" sourceLinked="1"/>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:txPr>
               <a:bodyPr/>
               <a:lstStyle/>
@@ -1922,6 +2425,7 @@
                 <a:pPr lvl="0">
                   <a:defRPr/>
                 </a:pPr>
+                <a:endParaRPr lang="en-CO"/>
               </a:p>
             </c:txPr>
             <c:showLegendKey val="0"/>
@@ -1930,19 +2434,61 @@
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
             <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="0"/>
+              </c:ext>
+            </c:extLst>
           </c:dLbls>
           <c:cat>
-            <c:strRef>
+            <c:numRef>
               <c:f>'Tecnológico  Geográfico 1'!$A$4:$A$7</c:f>
-            </c:strRef>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>2020</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2023</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
               <c:f>'Tecnológico  Geográfico 1'!$B$4:$B$7</c:f>
-              <c:numCache/>
+              <c:numCache>
+                <c:formatCode>#,##0</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>72797</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>79791</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>79431</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>80825</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-6302-C64C-B758-47E2A08414E5}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="1"/>
@@ -1950,6 +2496,12 @@
           <c:tx>
             <c:strRef>
               <c:f>'Tecnológico  Geográfico 1'!$C$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Oklahoma</c:v>
+                </c:pt>
+              </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
@@ -1974,7 +2526,13 @@
             </c:spPr>
           </c:marker>
           <c:dLbls>
-            <c:numFmt formatCode="General" sourceLinked="1"/>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:txPr>
               <a:bodyPr/>
               <a:lstStyle/>
@@ -1982,6 +2540,7 @@
                 <a:pPr lvl="0">
                   <a:defRPr/>
                 </a:pPr>
+                <a:endParaRPr lang="en-CO"/>
               </a:p>
             </c:txPr>
             <c:showLegendKey val="0"/>
@@ -1990,20 +2549,72 @@
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
             <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="0"/>
+              </c:ext>
+            </c:extLst>
           </c:dLbls>
           <c:cat>
-            <c:strRef>
+            <c:numRef>
               <c:f>'Tecnológico  Geográfico 1'!$A$4:$A$7</c:f>
-            </c:strRef>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>2020</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2023</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
               <c:f>'Tecnológico  Geográfico 1'!$C$4:$C$7</c:f>
-              <c:numCache/>
+              <c:numCache>
+                <c:formatCode>#,##0</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>42000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>44760</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>44566</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>45760</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-6302-C64C-B758-47E2A08414E5}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
         <c:axId val="1148608374"/>
         <c:axId val="782669609"/>
       </c:lineChart>
@@ -2029,7 +2640,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr b="0">
+                  <a:rPr lang="en-US" b="0">
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
@@ -2045,7 +2656,7 @@
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
-        <c:spPr/>
+        <c:tickLblPos val="nextTo"/>
         <c:txPr>
           <a:bodyPr/>
           <a:lstStyle/>
@@ -2058,9 +2669,15 @@
                 <a:latin typeface="+mn-lt"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="en-CO"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="782669609"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="1"/>
       </c:catAx>
       <c:valAx>
         <c:axId val="782669609"/>
@@ -2096,7 +2713,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr lvl="0">
-                  <a:defRPr b="0" sz="1000">
+                  <a:defRPr sz="1000" b="0">
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
@@ -2104,7 +2721,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr b="0" sz="1000">
+                  <a:rPr lang="en-US" sz="1000" b="0">
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
@@ -2117,7 +2734,7 @@
           </c:tx>
           <c:overlay val="0"/>
         </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="#,##0" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -2136,9 +2753,12 @@
                 <a:latin typeface="+mn-lt"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="en-CO"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="1148608374"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>
@@ -2156,16 +2776,28 @@
               <a:latin typeface="+mn-lt"/>
             </a:defRPr>
           </a:pPr>
+          <a:endParaRPr lang="en-CO"/>
         </a:p>
       </c:txPr>
     </c:legend>
     <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="zero"/>
+    <c:showDLblsOverMax val="1"/>
   </c:chart>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
 </c:chartSpace>
 </file>
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="1"/>
+  <c:style val="2"/>
   <c:chart>
     <c:title>
       <c:tx>
@@ -2182,7 +2814,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr b="0">
+              <a:rPr lang="en-US" b="0">
                 <a:solidFill>
                   <a:srgbClr val="757575"/>
                 </a:solidFill>
@@ -2196,21 +2828,30 @@
       </c:tx>
       <c:overlay val="0"/>
     </c:title>
+    <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
       <c:barChart>
         <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="1"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
               <c:f>'Tecnológico  Geográfico 2'!$A$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Variable</c:v>
+                </c:pt>
+              </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:schemeClr val="accent1"/>
+              <a:srgbClr val="4285F4"/>
             </a:solidFill>
             <a:ln cmpd="sng">
               <a:solidFill>
@@ -2218,18 +2859,65 @@
               </a:solidFill>
             </a:ln>
           </c:spPr>
+          <c:invertIfNegative val="1"/>
           <c:cat>
             <c:strRef>
               <c:f>('Tecnológico  Geográfico 2'!$B$3,'Tecnológico  Geográfico 2'!$C$3)</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>Missouri</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Oklahoma</c:v>
+                </c:pt>
+              </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
               <c:f>('Tecnológico  Geográfico 2'!$B$3,'Tecnológico  Geográfico 2'!$C$3)</c:f>
-              <c:numCache/>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{6F2FDCE9-48DA-4B69-8628-5D25D57E5C99}">
+              <c14:invertSolidFillFmt>
+                <c14:spPr xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF"/>
+                  </a:solidFill>
+                  <a:ln cmpd="sng">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                  </a:ln>
+                </c14:spPr>
+              </c14:invertSolidFillFmt>
+            </c:ext>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-6356-5843-BC7D-9647B512FCF4}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
         <c:axId val="37758144"/>
         <c:axId val="1391844348"/>
       </c:barChart>
@@ -2254,15 +2942,7 @@
                     <a:latin typeface="+mn-lt"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:r>
-                  <a:rPr b="0">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                  </a:rPr>
-                  <a:t/>
-                </a:r>
+                <a:endParaRPr lang="en-CO"/>
               </a:p>
             </c:rich>
           </c:tx>
@@ -2271,7 +2951,7 @@
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
-        <c:spPr/>
+        <c:tickLblPos val="nextTo"/>
         <c:txPr>
           <a:bodyPr/>
           <a:lstStyle/>
@@ -2284,9 +2964,15 @@
                 <a:latin typeface="+mn-lt"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="en-CO"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="1391844348"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="1"/>
       </c:catAx>
       <c:valAx>
         <c:axId val="1391844348"/>
@@ -2329,15 +3015,7 @@
                     <a:latin typeface="+mn-lt"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:r>
-                  <a:rPr b="0">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                  </a:rPr>
-                  <a:t/>
-                </a:r>
+                <a:endParaRPr lang="en-CO"/>
               </a:p>
             </c:rich>
           </c:tx>
@@ -2362,9 +3040,12 @@
                 <a:latin typeface="+mn-lt"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="en-CO"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="37758144"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>
@@ -2382,16 +3063,28 @@
               <a:latin typeface="+mn-lt"/>
             </a:defRPr>
           </a:pPr>
+          <a:endParaRPr lang="en-CO"/>
         </a:p>
       </c:txPr>
     </c:legend>
     <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="zero"/>
+    <c:showDLblsOverMax val="1"/>
   </c:chart>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
 </c:chartSpace>
 </file>
 
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="1"/>
+  <c:style val="2"/>
   <c:chart>
     <c:title>
       <c:tx>
@@ -2400,7 +3093,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr lvl="0">
-              <a:defRPr b="0" sz="1500">
+              <a:defRPr sz="1500" b="0">
                 <a:solidFill>
                   <a:srgbClr val="757575"/>
                 </a:solidFill>
@@ -2408,7 +3101,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr b="0" sz="1500">
+              <a:rPr lang="en-US" sz="1500" b="0">
                 <a:solidFill>
                   <a:srgbClr val="757575"/>
                 </a:solidFill>
@@ -2421,10 +3114,13 @@
       </c:tx>
       <c:overlay val="0"/>
     </c:title>
+    <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
       <c:barChart>
         <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="1"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
@@ -2433,7 +3129,7 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:schemeClr val="accent1"/>
+              <a:srgbClr val="4285F4"/>
             </a:solidFill>
             <a:ln cmpd="sng">
               <a:solidFill>
@@ -2441,11 +3137,25 @@
               </a:solidFill>
             </a:ln>
           </c:spPr>
+          <c:invertIfNegative val="1"/>
           <c:dPt>
             <c:idx val="0"/>
+            <c:invertIfNegative val="1"/>
+            <c:bubble3D val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000000-9B54-FA44-9C77-AC51A6C4E749}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dLbls>
-            <c:numFmt formatCode="General" sourceLinked="1"/>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:txPr>
               <a:bodyPr/>
               <a:lstStyle/>
@@ -2453,6 +3163,7 @@
                 <a:pPr lvl="0">
                   <a:defRPr/>
                 </a:pPr>
+                <a:endParaRPr lang="en-CO"/>
               </a:p>
             </c:txPr>
             <c:showLegendKey val="0"/>
@@ -2461,18 +3172,55 @@
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
             <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="0"/>
+              </c:ext>
+            </c:extLst>
           </c:dLbls>
           <c:cat>
             <c:strRef>
               <c:f>'Tecnológico  Geográfico 3'!$A$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Variable</c:v>
+                </c:pt>
+              </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
               <c:f>'Tecnológico  Geográfico 3'!$B$3</c:f>
-              <c:numCache/>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{6F2FDCE9-48DA-4B69-8628-5D25D57E5C99}">
+              <c14:invertSolidFillFmt>
+                <c14:spPr xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF"/>
+                  </a:solidFill>
+                  <a:ln cmpd="sng">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                  </a:ln>
+                </c14:spPr>
+              </c14:invertSolidFillFmt>
+            </c:ext>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-9B54-FA44-9C77-AC51A6C4E749}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="1"/>
@@ -2482,7 +3230,7 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:schemeClr val="accent2"/>
+              <a:srgbClr val="EA4335"/>
             </a:solidFill>
             <a:ln cmpd="sng">
               <a:solidFill>
@@ -2490,8 +3238,15 @@
               </a:solidFill>
             </a:ln>
           </c:spPr>
+          <c:invertIfNegative val="1"/>
           <c:dLbls>
-            <c:numFmt formatCode="General" sourceLinked="1"/>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:txPr>
               <a:bodyPr/>
               <a:lstStyle/>
@@ -2499,6 +3254,7 @@
                 <a:pPr lvl="0">
                   <a:defRPr/>
                 </a:pPr>
+                <a:endParaRPr lang="en-CO"/>
               </a:p>
             </c:txPr>
             <c:showLegendKey val="0"/>
@@ -2507,64 +3263,164 @@
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
             <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="0"/>
+              </c:ext>
+            </c:extLst>
           </c:dLbls>
           <c:cat>
             <c:strRef>
               <c:f>'Tecnológico  Geográfico 3'!$A$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Variable</c:v>
+                </c:pt>
+              </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
               <c:f>'Tecnológico  Geográfico 3'!$C$3</c:f>
-              <c:numCache/>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{6F2FDCE9-48DA-4B69-8628-5D25D57E5C99}">
+              <c14:invertSolidFillFmt>
+                <c14:spPr xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF"/>
+                  </a:solidFill>
+                  <a:ln cmpd="sng">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                  </a:ln>
+                </c14:spPr>
+              </c14:invertSolidFillFmt>
+            </c:ext>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-9B54-FA44-9C77-AC51A6C4E749}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="2"/>
           <c:order val="2"/>
+          <c:invertIfNegative val="1"/>
           <c:cat>
             <c:strRef>
               <c:f>'Tecnológico  Geográfico 3'!$A$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Variable</c:v>
+                </c:pt>
+              </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
               <c:f>'Tecnológico  Geográfico 3'!$A$4</c:f>
-              <c:numCache/>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-9B54-FA44-9C77-AC51A6C4E749}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="3"/>
           <c:order val="3"/>
+          <c:invertIfNegative val="1"/>
           <c:cat>
             <c:strRef>
               <c:f>'Tecnológico  Geográfico 3'!$A$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Variable</c:v>
+                </c:pt>
+              </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
               <c:f>'Tecnológico  Geográfico 3'!$B$4</c:f>
-              <c:numCache/>
+              <c:numCache>
+                <c:formatCode>#,##0</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>87887</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-9B54-FA44-9C77-AC51A6C4E749}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="4"/>
           <c:order val="4"/>
+          <c:invertIfNegative val="1"/>
           <c:cat>
             <c:strRef>
               <c:f>'Tecnológico  Geográfico 3'!$A$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Variable</c:v>
+                </c:pt>
+              </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
               <c:f>'Tecnológico  Geográfico 3'!$C$4</c:f>
-              <c:numCache/>
+              <c:numCache>
+                <c:formatCode>#,##0</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>70378</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-9B54-FA44-9C77-AC51A6C4E749}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
         <c:axId val="1040785516"/>
         <c:axId val="69678307"/>
       </c:barChart>
@@ -2590,7 +3446,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr b="0">
+                  <a:rPr lang="en-US" b="0">
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
@@ -2606,7 +3462,7 @@
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
-        <c:spPr/>
+        <c:tickLblPos val="nextTo"/>
         <c:txPr>
           <a:bodyPr/>
           <a:lstStyle/>
@@ -2619,9 +3475,15 @@
                 <a:latin typeface="+mn-lt"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="en-CO"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="69678307"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="1"/>
       </c:catAx>
       <c:valAx>
         <c:axId val="69678307"/>
@@ -2664,15 +3526,7 @@
                     <a:latin typeface="+mn-lt"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:r>
-                  <a:rPr b="0">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                  </a:rPr>
-                  <a:t/>
-                </a:r>
+                <a:endParaRPr lang="en-CO"/>
               </a:p>
             </c:rich>
           </c:tx>
@@ -2697,9 +3551,12 @@
                 <a:latin typeface="+mn-lt"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="en-CO"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="1040785516"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>
@@ -2717,16 +3574,28 @@
               <a:latin typeface="+mn-lt"/>
             </a:defRPr>
           </a:pPr>
+          <a:endParaRPr lang="en-CO"/>
         </a:p>
       </c:txPr>
     </c:legend>
     <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="zero"/>
+    <c:showDLblsOverMax val="1"/>
   </c:chart>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
 </c:chartSpace>
 </file>
 
 <file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="1"/>
+  <c:style val="2"/>
   <c:chart>
     <c:title>
       <c:tx>
@@ -2735,7 +3604,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr lvl="0">
-              <a:defRPr b="0" sz="1500">
+              <a:defRPr sz="1500" b="0">
                 <a:solidFill>
                   <a:srgbClr val="757575"/>
                 </a:solidFill>
@@ -2743,7 +3612,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr b="0" sz="1500">
+              <a:rPr lang="en-US" sz="1500" b="0">
                 <a:solidFill>
                   <a:srgbClr val="757575"/>
                 </a:solidFill>
@@ -2756,10 +3625,13 @@
       </c:tx>
       <c:overlay val="0"/>
     </c:title>
+    <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
       <c:barChart>
         <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="1"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
@@ -2768,7 +3640,7 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:schemeClr val="accent1"/>
+              <a:srgbClr val="4285F4"/>
             </a:solidFill>
             <a:ln cmpd="sng">
               <a:solidFill>
@@ -2776,8 +3648,15 @@
               </a:solidFill>
             </a:ln>
           </c:spPr>
+          <c:invertIfNegative val="1"/>
           <c:dLbls>
-            <c:numFmt formatCode="General" sourceLinked="1"/>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:txPr>
               <a:bodyPr/>
               <a:lstStyle/>
@@ -2785,6 +3664,7 @@
                 <a:pPr lvl="0">
                   <a:defRPr/>
                 </a:pPr>
+                <a:endParaRPr lang="en-CO"/>
               </a:p>
             </c:txPr>
             <c:showLegendKey val="0"/>
@@ -2793,18 +3673,55 @@
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
             <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="0"/>
+              </c:ext>
+            </c:extLst>
           </c:dLbls>
           <c:cat>
             <c:strRef>
               <c:f>'Tecnológico  Geográfico 3'!$A$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Variable</c:v>
+                </c:pt>
+              </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
               <c:f>'Tecnológico  Geográfico 3'!$B$3</c:f>
-              <c:numCache/>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{6F2FDCE9-48DA-4B69-8628-5D25D57E5C99}">
+              <c14:invertSolidFillFmt>
+                <c14:spPr xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF"/>
+                  </a:solidFill>
+                  <a:ln cmpd="sng">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                  </a:ln>
+                </c14:spPr>
+              </c14:invertSolidFillFmt>
+            </c:ext>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-675A-7346-BAD0-3016CBD86567}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="1"/>
@@ -2814,7 +3731,7 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:schemeClr val="accent2"/>
+              <a:srgbClr val="EA4335"/>
             </a:solidFill>
             <a:ln cmpd="sng">
               <a:solidFill>
@@ -2822,8 +3739,15 @@
               </a:solidFill>
             </a:ln>
           </c:spPr>
+          <c:invertIfNegative val="1"/>
           <c:dLbls>
-            <c:numFmt formatCode="General" sourceLinked="1"/>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:txPr>
               <a:bodyPr/>
               <a:lstStyle/>
@@ -2831,6 +3755,7 @@
                 <a:pPr lvl="0">
                   <a:defRPr/>
                 </a:pPr>
+                <a:endParaRPr lang="en-CO"/>
               </a:p>
             </c:txPr>
             <c:showLegendKey val="0"/>
@@ -2839,64 +3764,164 @@
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
             <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="0"/>
+              </c:ext>
+            </c:extLst>
           </c:dLbls>
           <c:cat>
             <c:strRef>
               <c:f>'Tecnológico  Geográfico 3'!$A$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Variable</c:v>
+                </c:pt>
+              </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
               <c:f>'Tecnológico  Geográfico 3'!$C$3</c:f>
-              <c:numCache/>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{6F2FDCE9-48DA-4B69-8628-5D25D57E5C99}">
+              <c14:invertSolidFillFmt>
+                <c14:spPr xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF"/>
+                  </a:solidFill>
+                  <a:ln cmpd="sng">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                  </a:ln>
+                </c14:spPr>
+              </c14:invertSolidFillFmt>
+            </c:ext>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-675A-7346-BAD0-3016CBD86567}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="2"/>
           <c:order val="2"/>
+          <c:invertIfNegative val="1"/>
           <c:cat>
             <c:strRef>
               <c:f>'Tecnológico  Geográfico 3'!$A$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Variable</c:v>
+                </c:pt>
+              </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
               <c:f>'Tecnológico  Geográfico 3'!$A$6</c:f>
-              <c:numCache/>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-675A-7346-BAD0-3016CBD86567}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="3"/>
           <c:order val="3"/>
+          <c:invertIfNegative val="1"/>
           <c:cat>
             <c:strRef>
               <c:f>'Tecnológico  Geográfico 3'!$A$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Variable</c:v>
+                </c:pt>
+              </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
               <c:f>'Tecnológico  Geográfico 3'!$B$6</c:f>
-              <c:numCache/>
+              <c:numCache>
+                <c:formatCode>#,##0</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>6610302</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-675A-7346-BAD0-3016CBD86567}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="4"/>
           <c:order val="4"/>
+          <c:invertIfNegative val="1"/>
           <c:cat>
             <c:strRef>
               <c:f>'Tecnológico  Geográfico 3'!$A$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Variable</c:v>
+                </c:pt>
+              </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
               <c:f>'Tecnológico  Geográfico 3'!$C$6</c:f>
-              <c:numCache/>
+              <c:numCache>
+                <c:formatCode>#,##0</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>18736254</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-675A-7346-BAD0-3016CBD86567}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
         <c:axId val="274330354"/>
         <c:axId val="802656595"/>
       </c:barChart>
@@ -2922,7 +3947,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr b="0">
+                  <a:rPr lang="en-US" b="0">
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
@@ -2938,7 +3963,7 @@
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
-        <c:spPr/>
+        <c:tickLblPos val="nextTo"/>
         <c:txPr>
           <a:bodyPr/>
           <a:lstStyle/>
@@ -2951,9 +3976,15 @@
                 <a:latin typeface="+mn-lt"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="en-CO"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="802656595"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="1"/>
       </c:catAx>
       <c:valAx>
         <c:axId val="802656595"/>
@@ -2996,15 +4027,7 @@
                     <a:latin typeface="+mn-lt"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:r>
-                  <a:rPr b="0">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                  </a:rPr>
-                  <a:t/>
-                </a:r>
+                <a:endParaRPr lang="en-CO"/>
               </a:p>
             </c:rich>
           </c:tx>
@@ -3029,9 +4052,12 @@
                 <a:latin typeface="+mn-lt"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="en-CO"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="274330354"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>
@@ -3049,20 +4075,235 @@
               <a:latin typeface="+mn-lt"/>
             </a:defRPr>
           </a:pPr>
+          <a:endParaRPr lang="en-CO"/>
         </a:p>
       </c:txPr>
     </c:legend>
     <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="zero"/>
+    <c:showDLblsOverMax val="1"/>
   </c:chart>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
 </c:chartSpace>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>95250</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="6276975" cy="3876675"/>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1" title="Gráfico">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing10.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>257175</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="5715000" cy="3533775"/>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 2" title="Gráfico">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="6105525" cy="3781425"/>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 3" title="Gráfico">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="5715000" cy="3533775"/>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart 4" title="Gráfico">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000004000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="3676650" cy="2276475"/>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Chart 5" title="Gráfico">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0800-000005000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>819150</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>219075</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="3743325" cy="2276475"/>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="6" name="Chart 6" title="Gráfico">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0800-000006000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
@@ -3070,14 +4311,63 @@
       <xdr:row>10</xdr:row>
       <xdr:rowOff>76200</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="5781675" cy="3733800"/>
+    <xdr:ext cx="5781675" cy="3730752"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image2.png" title="Imagen"/>
+        <xdr:cNvPr id="2" name="image2.png" title="Imagen">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0900-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="228600" y="1981200"/>
+          <a:ext cx="5781675" cy="3730752"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="5562600" cy="3629025"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="image3.png" title="Imagen">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0A00-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -3094,23 +4384,29 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing11.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
+<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
+      <xdr:colOff>923925</xdr:colOff>
       <xdr:row>9</xdr:row>
       <xdr:rowOff>28575</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="5562600" cy="3629025"/>
+    <xdr:ext cx="5133975" cy="3733800"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image3.png" title="Imagen"/>
+        <xdr:cNvPr id="2" name="image1.png" title="Imagen">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0B00-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -3127,49 +4423,8 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing12.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>923925</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="5133975" cy="3733800"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image1.png" title="Imagen"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing13.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing14.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing15.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
+<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>12</xdr:col>
@@ -3182,15 +4437,18 @@
       <xdr:nvPicPr>
         <xdr:cNvPr id="717131105" name="Chart7" title="Gráfico">
           <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0E00-0000618DBE2A}"/>
+            </a:ext>
             <a:ext uri="GoogleSheetsCustomDataVersion1">
-              <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" pictureOfChart="1"/>
+              <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="" pictureOfChart="1"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -3216,15 +4474,18 @@
       <xdr:nvPicPr>
         <xdr:cNvPr id="880302190" name="Chart8" title="Gráfico">
           <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0E00-00006E587834}"/>
+            </a:ext>
             <a:ext uri="GoogleSheetsCustomDataVersion1">
-              <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" pictureOfChart="1"/>
+              <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="" pictureOfChart="1"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -3241,209 +4502,18 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>95250</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="6276975" cy="3876675"/>
-    <xdr:graphicFrame>
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="1" name="Chart 1" title="Gráfico"/>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>257175</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="5715000" cy="3533775"/>
-    <xdr:graphicFrame>
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 2" title="Gráfico"/>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>19050</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="6105525" cy="3781425"/>
-    <xdr:graphicFrame>
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="3" name="Chart 3" title="Gráfico"/>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>133350</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="5715000" cy="3533775"/>
-    <xdr:graphicFrame>
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="4" name="Chart 4" title="Gráfico"/>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="3676650" cy="2276475"/>
-    <xdr:graphicFrame>
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="5" name="Chart 5" title="Gráfico"/>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>819150</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>219075</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="3743325" cy="2276475"/>
-    <xdr:graphicFrame>
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="6" name="Chart 6" title="Gráfico"/>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId2"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="B5:C9" displayName="Table_1" name="Table_1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table_1" displayName="Table_1" ref="B5:C9" headerRowCount="0">
   <tableColumns count="2">
-    <tableColumn name="Column1" id="1"/>
-    <tableColumn name="Column2" id="2"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Column1"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Column2"/>
   </tableColumns>
-  <tableStyleInfo name="SOCIALcultural 1-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+  <tableStyleInfo name="SOCIALcultural 1-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -3633,32 +4703,38 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:J23"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="10.88"/>
-    <col customWidth="1" min="4" max="4" width="33.13"/>
-    <col customWidth="1" min="6" max="6" width="45.88"/>
+    <col min="1" max="1" width="10.83203125" customWidth="1"/>
+    <col min="4" max="4" width="33.1640625" customWidth="1"/>
+    <col min="6" max="6" width="45.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A1" s="47" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2">
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+    </row>
+    <row r="2" spans="1:10" ht="15.75" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:10" ht="15.75" customHeight="1">
       <c r="A3" s="3"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -3666,7 +4742,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:10" ht="15.75" customHeight="1">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -3674,7 +4750,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:10" ht="15.75" customHeight="1">
       <c r="A5" s="3"/>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -3682,12 +4758,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:10" ht="15.75" customHeight="1">
       <c r="A6" s="3"/>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
     </row>
-    <row r="7">
+    <row r="7" spans="1:10" ht="15.75" customHeight="1">
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
@@ -3695,101 +4771,107 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:10" ht="15.75" customHeight="1">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
-      <c r="F8" s="4" t="s">
+      <c r="F8" s="49" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="9">
-      <c r="F9" s="2"/>
-    </row>
-    <row r="12">
-      <c r="F12" s="5" t="s">
+      <c r="G8" s="48"/>
+      <c r="H8" s="48"/>
+      <c r="I8" s="48"/>
+    </row>
+    <row r="9" spans="1:10" ht="15.75" customHeight="1">
+      <c r="F9" s="50"/>
+      <c r="G9" s="48"/>
+      <c r="H9" s="48"/>
+      <c r="I9" s="48"/>
+    </row>
+    <row r="12" spans="1:10" ht="15.75" customHeight="1">
+      <c r="F12" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="13">
-      <c r="F13" s="6" t="s">
+    <row r="13" spans="1:10" ht="15.75" customHeight="1">
+      <c r="F13" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6"/>
-      <c r="I13" s="6"/>
-      <c r="J13" s="6"/>
-    </row>
-    <row r="14">
-      <c r="F14" s="6"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
-      <c r="I14" s="6"/>
-      <c r="J14" s="6"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="6"/>
-      <c r="F15" s="6"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="6"/>
-      <c r="I15" s="6"/>
-      <c r="J15" s="6"/>
-    </row>
-    <row r="16">
-      <c r="F16" s="6"/>
-      <c r="G16" s="6"/>
-      <c r="H16" s="6"/>
-      <c r="I16" s="6"/>
-      <c r="J16" s="6"/>
-    </row>
-    <row r="17">
-      <c r="F17" s="6"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="6"/>
-      <c r="I17" s="6"/>
-      <c r="J17" s="6"/>
-    </row>
-    <row r="18">
-      <c r="F18" s="6"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="6"/>
-      <c r="I18" s="6"/>
-      <c r="J18" s="6"/>
-    </row>
-    <row r="19">
-      <c r="F19" s="6"/>
-      <c r="G19" s="6"/>
-      <c r="H19" s="6"/>
-      <c r="I19" s="6"/>
-      <c r="J19" s="6"/>
-    </row>
-    <row r="20">
-      <c r="F20" s="6"/>
-      <c r="G20" s="6"/>
-      <c r="H20" s="6"/>
-      <c r="I20" s="6"/>
-      <c r="J20" s="6"/>
-    </row>
-    <row r="21">
-      <c r="F21" s="6"/>
-      <c r="G21" s="6"/>
-      <c r="H21" s="6"/>
-      <c r="I21" s="6"/>
-      <c r="J21" s="6"/>
-    </row>
-    <row r="22">
-      <c r="F22" s="6"/>
-      <c r="G22" s="6"/>
-      <c r="H22" s="6"/>
-      <c r="I22" s="6"/>
-      <c r="J22" s="6"/>
-    </row>
-    <row r="23">
-      <c r="F23" s="6"/>
-      <c r="G23" s="6"/>
-      <c r="H23" s="6"/>
-      <c r="I23" s="6"/>
-      <c r="J23" s="6"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="5"/>
+    </row>
+    <row r="14" spans="1:10" ht="15.75" customHeight="1">
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="5"/>
+    </row>
+    <row r="15" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="5"/>
+    </row>
+    <row r="16" spans="1:10" ht="15.75" customHeight="1">
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="5"/>
+    </row>
+    <row r="17" spans="6:10" ht="15.75" customHeight="1">
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="5"/>
+      <c r="J17" s="5"/>
+    </row>
+    <row r="18" spans="6:10" ht="15.75" customHeight="1">
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
+      <c r="J18" s="5"/>
+    </row>
+    <row r="19" spans="6:10" ht="15.75" customHeight="1">
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="5"/>
+      <c r="J19" s="5"/>
+    </row>
+    <row r="20" spans="6:10" ht="15.75" customHeight="1">
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="5"/>
+      <c r="J20" s="5"/>
+    </row>
+    <row r="21" spans="6:10" ht="15.75" customHeight="1">
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
+      <c r="I21" s="5"/>
+      <c r="J21" s="5"/>
+    </row>
+    <row r="22" spans="6:10" ht="15.75" customHeight="1">
+      <c r="F22" s="5"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5"/>
+      <c r="I22" s="5"/>
+      <c r="J22" s="5"/>
+    </row>
+    <row r="23" spans="6:10" ht="15.75" customHeight="1">
+      <c r="F23" s="5"/>
+      <c r="G23" s="5"/>
+      <c r="H23" s="5"/>
+      <c r="I23" s="5"/>
+      <c r="J23" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -3798,199 +4880,209 @@
     <mergeCell ref="F9:I9"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink r:id="rId1" ref="F8"/>
+    <hyperlink ref="F8" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
   </hyperlinks>
-  <drawing r:id="rId2"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:J23"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="10.88"/>
-    <col customWidth="1" min="4" max="4" width="33.13"/>
-    <col customWidth="1" min="6" max="6" width="46.0"/>
+    <col min="1" max="1" width="10.83203125" customWidth="1"/>
+    <col min="4" max="4" width="33.1640625" customWidth="1"/>
+    <col min="6" max="6" width="46" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="2">
+    <row r="1" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A1" s="47" t="s">
+        <v>79</v>
+      </c>
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+    </row>
+    <row r="2" spans="1:10" ht="15.75" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="34" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A3" s="27" t="s">
         <v>49</v>
       </c>
-      <c r="B3" s="34" t="s">
+      <c r="B3" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="34" t="s">
+      <c r="C3" s="27" t="s">
         <v>18</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="35">
-        <v>2021.0</v>
-      </c>
-      <c r="B4" s="36" t="s">
+    <row r="4" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A4" s="28">
+        <v>2021</v>
+      </c>
+      <c r="B4" s="29" t="s">
+        <v>81</v>
+      </c>
+      <c r="C4" s="29" t="s">
+        <v>82</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A5" s="28">
+        <v>2022</v>
+      </c>
+      <c r="B5" s="29" t="s">
+        <v>83</v>
+      </c>
+      <c r="C5" s="29" t="s">
+        <v>84</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A6" s="28">
+        <v>2023</v>
+      </c>
+      <c r="B6" s="29" t="s">
+        <v>85</v>
+      </c>
+      <c r="C6" s="29" t="s">
         <v>86</v>
       </c>
-      <c r="C4" s="36" t="s">
+    </row>
+    <row r="7" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A7" s="35">
+        <v>2024</v>
+      </c>
+      <c r="B7" s="36" t="s">
+        <v>85</v>
+      </c>
+      <c r="C7" s="36" t="s">
         <v>87</v>
       </c>
-      <c r="F4" s="3" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="35">
-        <v>2022.0</v>
-      </c>
-      <c r="B5" s="36" t="s">
-        <v>89</v>
-      </c>
-      <c r="C5" s="36" t="s">
-        <v>90</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="35">
-        <v>2023.0</v>
-      </c>
-      <c r="B6" s="36" t="s">
-        <v>92</v>
-      </c>
-      <c r="C6" s="36" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="44">
-        <v>2024.0</v>
-      </c>
-      <c r="B7" s="45" t="s">
-        <v>92</v>
-      </c>
-      <c r="C7" s="45" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="46"/>
-      <c r="B8" s="48"/>
-      <c r="C8" s="48"/>
-      <c r="D8" s="49"/>
+    </row>
+    <row r="8" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A8" s="37"/>
+      <c r="B8" s="39"/>
+      <c r="C8" s="39"/>
+      <c r="D8" s="40"/>
       <c r="F8" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9">
-      <c r="F9" s="23" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="8"/>
-    </row>
-    <row r="12">
-      <c r="F12" s="5" t="s">
+    <row r="9" spans="1:10" ht="15.75" customHeight="1">
+      <c r="F9" s="56" t="s">
+        <v>88</v>
+      </c>
+      <c r="G9" s="48"/>
+      <c r="H9" s="48"/>
+      <c r="I9" s="48"/>
+    </row>
+    <row r="11" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A11" s="50"/>
+      <c r="B11" s="48"/>
+      <c r="C11" s="48"/>
+      <c r="D11" s="48"/>
+    </row>
+    <row r="12" spans="1:10" ht="15.75" customHeight="1">
+      <c r="F12" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="13">
-      <c r="F13" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6"/>
-      <c r="I13" s="6"/>
-      <c r="J13" s="6"/>
-    </row>
-    <row r="14">
-      <c r="F14" s="6"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
-      <c r="I14" s="6"/>
-      <c r="J14" s="6"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="6"/>
-      <c r="F15" s="6"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="6"/>
-      <c r="I15" s="6"/>
-      <c r="J15" s="6"/>
-    </row>
-    <row r="16">
-      <c r="F16" s="6"/>
-      <c r="G16" s="6"/>
-      <c r="H16" s="6"/>
-      <c r="I16" s="6"/>
-      <c r="J16" s="6"/>
-    </row>
-    <row r="17">
-      <c r="F17" s="6"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="6"/>
-      <c r="I17" s="6"/>
-      <c r="J17" s="6"/>
-    </row>
-    <row r="18">
-      <c r="F18" s="6"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="6"/>
-      <c r="I18" s="6"/>
-      <c r="J18" s="6"/>
-    </row>
-    <row r="19">
-      <c r="F19" s="6"/>
-      <c r="G19" s="6"/>
-      <c r="H19" s="6"/>
-      <c r="I19" s="6"/>
-      <c r="J19" s="6"/>
-    </row>
-    <row r="20">
-      <c r="F20" s="6"/>
-      <c r="G20" s="6"/>
-      <c r="H20" s="6"/>
-      <c r="I20" s="6"/>
-      <c r="J20" s="6"/>
-    </row>
-    <row r="21">
-      <c r="F21" s="6"/>
-      <c r="G21" s="6"/>
-      <c r="H21" s="6"/>
-      <c r="I21" s="6"/>
-      <c r="J21" s="6"/>
-    </row>
-    <row r="22">
-      <c r="F22" s="6"/>
-      <c r="G22" s="6"/>
-      <c r="H22" s="6"/>
-      <c r="I22" s="6"/>
-      <c r="J22" s="6"/>
-    </row>
-    <row r="23">
-      <c r="F23" s="6"/>
-      <c r="G23" s="6"/>
-      <c r="H23" s="6"/>
-      <c r="I23" s="6"/>
-      <c r="J23" s="6"/>
+    <row r="13" spans="1:10" ht="15.75" customHeight="1">
+      <c r="F13" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="5"/>
+    </row>
+    <row r="14" spans="1:10" ht="15.75" customHeight="1">
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="5"/>
+    </row>
+    <row r="15" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="5"/>
+    </row>
+    <row r="16" spans="1:10" ht="15.75" customHeight="1">
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="5"/>
+    </row>
+    <row r="17" spans="6:10" ht="15.75" customHeight="1">
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="5"/>
+      <c r="J17" s="5"/>
+    </row>
+    <row r="18" spans="6:10" ht="15.75" customHeight="1">
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
+      <c r="J18" s="5"/>
+    </row>
+    <row r="19" spans="6:10" ht="15.75" customHeight="1">
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="5"/>
+      <c r="J19" s="5"/>
+    </row>
+    <row r="20" spans="6:10" ht="15.75" customHeight="1">
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="5"/>
+      <c r="J20" s="5"/>
+    </row>
+    <row r="21" spans="6:10" ht="15.75" customHeight="1">
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
+      <c r="I21" s="5"/>
+      <c r="J21" s="5"/>
+    </row>
+    <row r="22" spans="6:10" ht="15.75" customHeight="1">
+      <c r="F22" s="5"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5"/>
+      <c r="I22" s="5"/>
+      <c r="J22" s="5"/>
+    </row>
+    <row r="23" spans="6:10" ht="15.75" customHeight="1">
+      <c r="F23" s="5"/>
+      <c r="G23" s="5"/>
+      <c r="H23" s="5"/>
+      <c r="I23" s="5"/>
+      <c r="J23" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -3999,200 +5091,211 @@
     <mergeCell ref="A11:D11"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink r:id="rId1" ref="F9"/>
+    <hyperlink ref="F9" r:id="rId1" xr:uid="{00000000-0004-0000-0900-000000000000}"/>
   </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:J23"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="10.88"/>
-    <col customWidth="1" min="2" max="2" width="13.88"/>
-    <col customWidth="1" min="3" max="3" width="14.5"/>
-    <col customWidth="1" min="4" max="4" width="33.13"/>
-    <col customWidth="1" min="6" max="6" width="46.0"/>
+    <col min="1" max="1" width="10.83203125" customWidth="1"/>
+    <col min="2" max="2" width="13.83203125" customWidth="1"/>
+    <col min="3" max="3" width="14.5" customWidth="1"/>
+    <col min="4" max="4" width="33.1640625" customWidth="1"/>
+    <col min="6" max="6" width="46" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="2">
+    <row r="1" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A1" s="47" t="s">
+        <v>90</v>
+      </c>
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+    </row>
+    <row r="2" spans="1:10" ht="15.75" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="34" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A3" s="27" t="s">
         <v>49</v>
       </c>
-      <c r="B3" s="34" t="s">
-        <v>99</v>
-      </c>
-      <c r="C3" s="34" t="s">
-        <v>100</v>
+      <c r="B3" s="27" t="s">
+        <v>92</v>
+      </c>
+      <c r="C3" s="27" t="s">
+        <v>93</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="35">
-        <v>2021.0</v>
-      </c>
-      <c r="B4" s="50">
-        <v>0.037</v>
-      </c>
-      <c r="C4" s="50">
-        <v>0.025</v>
+    <row r="4" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A4" s="28">
+        <v>2021</v>
+      </c>
+      <c r="B4" s="41">
+        <v>3.6999999999999998E-2</v>
+      </c>
+      <c r="C4" s="41">
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="35">
-        <v>2022.0</v>
-      </c>
-      <c r="B5" s="50">
-        <v>0.041</v>
-      </c>
-      <c r="C5" s="50">
-        <v>0.029</v>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A5" s="28">
+        <v>2022</v>
+      </c>
+      <c r="B5" s="41">
+        <v>4.1000000000000002E-2</v>
+      </c>
+      <c r="C5" s="41">
+        <v>2.9000000000000001E-2</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="35">
-        <v>2023.0</v>
-      </c>
-      <c r="B6" s="50">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A6" s="28">
+        <v>2023</v>
+      </c>
+      <c r="B6" s="41">
         <v>0.04</v>
       </c>
-      <c r="C6" s="50">
-        <v>0.026</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="44">
-        <v>2024.0</v>
-      </c>
-      <c r="B7" s="51">
-        <v>0.043</v>
-      </c>
-      <c r="C7" s="51">
-        <v>0.029</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="46"/>
-      <c r="B8" s="48"/>
-      <c r="C8" s="48"/>
+      <c r="C6" s="41">
+        <v>2.5999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A7" s="35">
+        <v>2024</v>
+      </c>
+      <c r="B7" s="42">
+        <v>4.2999999999999997E-2</v>
+      </c>
+      <c r="C7" s="42">
+        <v>2.9000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A8" s="37"/>
+      <c r="B8" s="39"/>
+      <c r="C8" s="39"/>
       <c r="F8" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9">
-      <c r="F9" s="23" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="8"/>
-    </row>
-    <row r="12">
-      <c r="F12" s="5" t="s">
+    <row r="9" spans="1:10" ht="15.75" customHeight="1">
+      <c r="F9" s="56" t="s">
+        <v>94</v>
+      </c>
+      <c r="G9" s="48"/>
+      <c r="H9" s="48"/>
+      <c r="I9" s="48"/>
+    </row>
+    <row r="11" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A11" s="50"/>
+      <c r="B11" s="48"/>
+      <c r="C11" s="48"/>
+      <c r="D11" s="48"/>
+    </row>
+    <row r="12" spans="1:10" ht="15.75" customHeight="1">
+      <c r="F12" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="13">
-      <c r="F13" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6"/>
-      <c r="I13" s="6"/>
-      <c r="J13" s="6"/>
-    </row>
-    <row r="14">
-      <c r="F14" s="6"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
-      <c r="I14" s="6"/>
-      <c r="J14" s="6"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="6"/>
-      <c r="F15" s="6"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="6"/>
-      <c r="I15" s="6"/>
-      <c r="J15" s="6"/>
-    </row>
-    <row r="16">
-      <c r="F16" s="6"/>
-      <c r="G16" s="6"/>
-      <c r="H16" s="6"/>
-      <c r="I16" s="6"/>
-      <c r="J16" s="6"/>
-    </row>
-    <row r="17">
-      <c r="F17" s="6"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="6"/>
-      <c r="I17" s="6"/>
-      <c r="J17" s="6"/>
-    </row>
-    <row r="18">
-      <c r="F18" s="6"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="6"/>
-      <c r="I18" s="6"/>
-      <c r="J18" s="6"/>
-    </row>
-    <row r="19">
-      <c r="F19" s="6"/>
-      <c r="G19" s="6"/>
-      <c r="H19" s="6"/>
-      <c r="I19" s="6"/>
-      <c r="J19" s="6"/>
-    </row>
-    <row r="20">
-      <c r="F20" s="6"/>
-      <c r="G20" s="6"/>
-      <c r="H20" s="6"/>
-      <c r="I20" s="6"/>
-      <c r="J20" s="6"/>
-    </row>
-    <row r="21">
-      <c r="F21" s="6"/>
-      <c r="G21" s="6"/>
-      <c r="H21" s="6"/>
-      <c r="I21" s="6"/>
-      <c r="J21" s="6"/>
-    </row>
-    <row r="22">
-      <c r="F22" s="6"/>
-      <c r="G22" s="6"/>
-      <c r="H22" s="6"/>
-      <c r="I22" s="6"/>
-      <c r="J22" s="6"/>
-    </row>
-    <row r="23">
-      <c r="F23" s="6"/>
-      <c r="G23" s="6"/>
-      <c r="H23" s="6"/>
-      <c r="I23" s="6"/>
-      <c r="J23" s="6"/>
+    <row r="13" spans="1:10" ht="15.75" customHeight="1">
+      <c r="F13" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="5"/>
+    </row>
+    <row r="14" spans="1:10" ht="15.75" customHeight="1">
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="5"/>
+    </row>
+    <row r="15" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="5"/>
+    </row>
+    <row r="16" spans="1:10" ht="15.75" customHeight="1">
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="5"/>
+    </row>
+    <row r="17" spans="6:10" ht="15.75" customHeight="1">
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="5"/>
+      <c r="J17" s="5"/>
+    </row>
+    <row r="18" spans="6:10" ht="15.75" customHeight="1">
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
+      <c r="J18" s="5"/>
+    </row>
+    <row r="19" spans="6:10" ht="15.75" customHeight="1">
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="5"/>
+      <c r="J19" s="5"/>
+    </row>
+    <row r="20" spans="6:10" ht="15.75" customHeight="1">
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="5"/>
+      <c r="J20" s="5"/>
+    </row>
+    <row r="21" spans="6:10" ht="15.75" customHeight="1">
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
+      <c r="I21" s="5"/>
+      <c r="J21" s="5"/>
+    </row>
+    <row r="22" spans="6:10" ht="15.75" customHeight="1">
+      <c r="F22" s="5"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5"/>
+      <c r="I22" s="5"/>
+      <c r="J22" s="5"/>
+    </row>
+    <row r="23" spans="6:10" ht="15.75" customHeight="1">
+      <c r="F23" s="5"/>
+      <c r="G23" s="5"/>
+      <c r="H23" s="5"/>
+      <c r="I23" s="5"/>
+      <c r="J23" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -4201,198 +5304,209 @@
     <mergeCell ref="A11:D11"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink r:id="rId1" ref="F9"/>
+    <hyperlink ref="F9" r:id="rId1" xr:uid="{00000000-0004-0000-0A00-000000000000}"/>
   </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:J23"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="31.75"/>
-    <col customWidth="1" min="4" max="4" width="33.13"/>
-    <col customWidth="1" min="6" max="6" width="46.0"/>
+    <col min="1" max="1" width="31.6640625" customWidth="1"/>
+    <col min="4" max="4" width="33.1640625" customWidth="1"/>
+    <col min="6" max="6" width="46" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="2">
+    <row r="1" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A1" s="47" t="s">
+        <v>96</v>
+      </c>
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+    </row>
+    <row r="2" spans="1:10" ht="15.75" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="34" t="s">
-        <v>106</v>
-      </c>
-      <c r="B3" s="34" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A3" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="B3" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="34" t="s">
+      <c r="C3" s="27" t="s">
         <v>18</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="35" t="s">
+    <row r="4" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A4" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="B4" s="29">
+        <v>99</v>
+      </c>
+      <c r="C4" s="29">
+        <v>46</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A5" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="B5" s="29">
+        <v>5842</v>
+      </c>
+      <c r="C5" s="29">
+        <v>2974</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A6" s="28" t="s">
+        <v>103</v>
+      </c>
+      <c r="B6" s="29" t="s">
+        <v>104</v>
+      </c>
+      <c r="C6" s="29" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A7" s="35" t="s">
+        <v>106</v>
+      </c>
+      <c r="B7" s="36" t="s">
         <v>107</v>
       </c>
-      <c r="B4" s="36">
-        <v>99.0</v>
-      </c>
-      <c r="C4" s="36">
-        <v>46.0</v>
-      </c>
-      <c r="F4" s="3" t="s">
+      <c r="C7" s="36" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="35" t="s">
-        <v>109</v>
-      </c>
-      <c r="B5" s="36">
-        <v>5842.0</v>
-      </c>
-      <c r="C5" s="36">
-        <v>2974.0</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="35" t="s">
-        <v>111</v>
-      </c>
-      <c r="B6" s="36" t="s">
-        <v>112</v>
-      </c>
-      <c r="C6" s="36" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="44" t="s">
-        <v>114</v>
-      </c>
-      <c r="B7" s="45" t="s">
-        <v>115</v>
-      </c>
-      <c r="C7" s="45" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="46"/>
-      <c r="B8" s="48"/>
-      <c r="C8" s="48"/>
+    <row r="8" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A8" s="37"/>
+      <c r="B8" s="39"/>
+      <c r="C8" s="39"/>
       <c r="F8" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9">
-      <c r="F9" s="23" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="8"/>
-    </row>
-    <row r="12">
-      <c r="F12" s="5" t="s">
+    <row r="9" spans="1:10" ht="15.75" customHeight="1">
+      <c r="F9" s="56" t="s">
+        <v>109</v>
+      </c>
+      <c r="G9" s="48"/>
+      <c r="H9" s="48"/>
+      <c r="I9" s="48"/>
+    </row>
+    <row r="11" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A11" s="50"/>
+      <c r="B11" s="48"/>
+      <c r="C11" s="48"/>
+      <c r="D11" s="48"/>
+    </row>
+    <row r="12" spans="1:10" ht="15.75" customHeight="1">
+      <c r="F12" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="13">
-      <c r="F13" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6"/>
-      <c r="I13" s="6"/>
-      <c r="J13" s="6"/>
-    </row>
-    <row r="14">
-      <c r="F14" s="6"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
-      <c r="I14" s="6"/>
-      <c r="J14" s="6"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="6"/>
-      <c r="F15" s="6"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="6"/>
-      <c r="I15" s="6"/>
-      <c r="J15" s="6"/>
-    </row>
-    <row r="16">
-      <c r="F16" s="6"/>
-      <c r="G16" s="6"/>
-      <c r="H16" s="6"/>
-      <c r="I16" s="6"/>
-      <c r="J16" s="6"/>
-    </row>
-    <row r="17">
-      <c r="F17" s="6"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="6"/>
-      <c r="I17" s="6"/>
-      <c r="J17" s="6"/>
-    </row>
-    <row r="18">
-      <c r="F18" s="6"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="6"/>
-      <c r="I18" s="6"/>
-      <c r="J18" s="6"/>
-    </row>
-    <row r="19">
-      <c r="F19" s="6"/>
-      <c r="G19" s="6"/>
-      <c r="H19" s="6"/>
-      <c r="I19" s="6"/>
-      <c r="J19" s="6"/>
-    </row>
-    <row r="20">
-      <c r="F20" s="6"/>
-      <c r="G20" s="6"/>
-      <c r="H20" s="6"/>
-      <c r="I20" s="6"/>
-      <c r="J20" s="6"/>
-    </row>
-    <row r="21">
-      <c r="F21" s="6"/>
-      <c r="G21" s="6"/>
-      <c r="H21" s="6"/>
-      <c r="I21" s="6"/>
-      <c r="J21" s="6"/>
-    </row>
-    <row r="22">
-      <c r="F22" s="6"/>
-      <c r="G22" s="6"/>
-      <c r="H22" s="6"/>
-      <c r="I22" s="6"/>
-      <c r="J22" s="6"/>
-    </row>
-    <row r="23">
-      <c r="F23" s="6"/>
-      <c r="G23" s="6"/>
-      <c r="H23" s="6"/>
-      <c r="I23" s="6"/>
-      <c r="J23" s="6"/>
+    <row r="13" spans="1:10" ht="15.75" customHeight="1">
+      <c r="F13" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="5"/>
+    </row>
+    <row r="14" spans="1:10" ht="15.75" customHeight="1">
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="5"/>
+    </row>
+    <row r="15" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="5"/>
+    </row>
+    <row r="16" spans="1:10" ht="15.75" customHeight="1">
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="5"/>
+    </row>
+    <row r="17" spans="6:10" ht="15.75" customHeight="1">
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="5"/>
+      <c r="J17" s="5"/>
+    </row>
+    <row r="18" spans="6:10" ht="15.75" customHeight="1">
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
+      <c r="J18" s="5"/>
+    </row>
+    <row r="19" spans="6:10" ht="15.75" customHeight="1">
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="5"/>
+      <c r="J19" s="5"/>
+    </row>
+    <row r="20" spans="6:10" ht="15.75" customHeight="1">
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="5"/>
+      <c r="J20" s="5"/>
+    </row>
+    <row r="21" spans="6:10" ht="15.75" customHeight="1">
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
+      <c r="I21" s="5"/>
+      <c r="J21" s="5"/>
+    </row>
+    <row r="22" spans="6:10" ht="15.75" customHeight="1">
+      <c r="F22" s="5"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5"/>
+      <c r="I22" s="5"/>
+      <c r="J22" s="5"/>
+    </row>
+    <row r="23" spans="6:10" ht="15.75" customHeight="1">
+      <c r="F23" s="5"/>
+      <c r="G23" s="5"/>
+      <c r="H23" s="5"/>
+      <c r="I23" s="5"/>
+      <c r="J23" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -4401,138 +5515,149 @@
     <mergeCell ref="A11:D11"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink r:id="rId1" ref="F9"/>
+    <hyperlink ref="F9" r:id="rId1" xr:uid="{00000000-0004-0000-0B00-000000000000}"/>
   </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:J23"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="19.0"/>
-    <col customWidth="1" min="2" max="2" width="7.63"/>
-    <col customWidth="1" min="4" max="4" width="33.13"/>
-    <col customWidth="1" min="6" max="6" width="49.0"/>
+    <col min="1" max="1" width="19" customWidth="1"/>
+    <col min="2" max="2" width="7.6640625" customWidth="1"/>
+    <col min="4" max="4" width="33.1640625" customWidth="1"/>
+    <col min="6" max="6" width="49" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="F2" s="52" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="F4" s="23" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="5">
+    <row r="1" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A1" s="47" t="s">
+        <v>111</v>
+      </c>
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+    </row>
+    <row r="2" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A2" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="F2" s="43" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="15.75" customHeight="1">
+      <c r="F4" s="16" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="15.75" customHeight="1">
       <c r="C5" s="3"/>
     </row>
-    <row r="7">
-      <c r="F7" s="5" t="s">
+    <row r="7" spans="1:10" ht="15.75" customHeight="1">
+      <c r="F7" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8">
-      <c r="F8" s="6" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="F9" s="8"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="8"/>
-    </row>
-    <row r="13">
-      <c r="G13" s="6"/>
-      <c r="H13" s="6"/>
-      <c r="I13" s="6"/>
-      <c r="J13" s="6"/>
-    </row>
-    <row r="14">
-      <c r="F14" s="6"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
-      <c r="I14" s="6"/>
-      <c r="J14" s="6"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="6"/>
-      <c r="F15" s="6"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="6"/>
-      <c r="I15" s="6"/>
-      <c r="J15" s="6"/>
-    </row>
-    <row r="16">
-      <c r="F16" s="6"/>
-      <c r="G16" s="6"/>
-      <c r="H16" s="6"/>
-      <c r="I16" s="6"/>
-      <c r="J16" s="6"/>
-    </row>
-    <row r="17">
-      <c r="F17" s="6"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="6"/>
-      <c r="I17" s="6"/>
-      <c r="J17" s="6"/>
-    </row>
-    <row r="18">
-      <c r="F18" s="6"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="6"/>
-      <c r="I18" s="6"/>
-      <c r="J18" s="6"/>
-    </row>
-    <row r="19">
-      <c r="F19" s="6"/>
-      <c r="G19" s="6"/>
-      <c r="H19" s="6"/>
-      <c r="I19" s="6"/>
-      <c r="J19" s="6"/>
-    </row>
-    <row r="20">
-      <c r="F20" s="6"/>
-      <c r="G20" s="6"/>
-      <c r="H20" s="6"/>
-      <c r="I20" s="6"/>
-      <c r="J20" s="6"/>
-    </row>
-    <row r="21">
-      <c r="F21" s="6"/>
-      <c r="G21" s="6"/>
-      <c r="H21" s="6"/>
-      <c r="I21" s="6"/>
-      <c r="J21" s="6"/>
-    </row>
-    <row r="22">
-      <c r="F22" s="6"/>
-      <c r="G22" s="6"/>
-      <c r="H22" s="6"/>
-      <c r="I22" s="6"/>
-      <c r="J22" s="6"/>
-    </row>
-    <row r="23">
-      <c r="F23" s="6"/>
-      <c r="G23" s="6"/>
-      <c r="H23" s="6"/>
-      <c r="I23" s="6"/>
-      <c r="J23" s="6"/>
+    <row r="8" spans="1:10" ht="15.75" customHeight="1">
+      <c r="F8" s="5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="15.75" customHeight="1">
+      <c r="F9" s="50"/>
+      <c r="G9" s="48"/>
+      <c r="H9" s="48"/>
+      <c r="I9" s="48"/>
+    </row>
+    <row r="11" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A11" s="50"/>
+      <c r="B11" s="48"/>
+      <c r="C11" s="48"/>
+      <c r="D11" s="48"/>
+    </row>
+    <row r="13" spans="1:10" ht="15.75" customHeight="1">
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="5"/>
+    </row>
+    <row r="14" spans="1:10" ht="15.75" customHeight="1">
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="5"/>
+    </row>
+    <row r="15" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="5"/>
+    </row>
+    <row r="16" spans="1:10" ht="15.75" customHeight="1">
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="5"/>
+    </row>
+    <row r="17" spans="6:10" ht="15.75" customHeight="1">
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="5"/>
+      <c r="J17" s="5"/>
+    </row>
+    <row r="18" spans="6:10" ht="15.75" customHeight="1">
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
+      <c r="J18" s="5"/>
+    </row>
+    <row r="19" spans="6:10" ht="15.75" customHeight="1">
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="5"/>
+      <c r="J19" s="5"/>
+    </row>
+    <row r="20" spans="6:10" ht="15.75" customHeight="1">
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="5"/>
+      <c r="J20" s="5"/>
+    </row>
+    <row r="21" spans="6:10" ht="15.75" customHeight="1">
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
+      <c r="I21" s="5"/>
+      <c r="J21" s="5"/>
+    </row>
+    <row r="22" spans="6:10" ht="15.75" customHeight="1">
+      <c r="F22" s="5"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5"/>
+      <c r="I22" s="5"/>
+      <c r="J22" s="5"/>
+    </row>
+    <row r="23" spans="6:10" ht="15.75" customHeight="1">
+      <c r="F23" s="5"/>
+      <c r="G23" s="5"/>
+      <c r="H23" s="5"/>
+      <c r="I23" s="5"/>
+      <c r="J23" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -4541,142 +5666,152 @@
     <mergeCell ref="A11:D11"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink r:id="rId1" ref="F4"/>
+    <hyperlink ref="F4" r:id="rId1" xr:uid="{00000000-0004-0000-0C00-000000000000}"/>
   </hyperlinks>
-  <drawing r:id="rId2"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:J23"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="10.88"/>
-    <col customWidth="1" min="4" max="4" width="33.13"/>
-    <col customWidth="1" min="6" max="6" width="46.0"/>
+    <col min="1" max="1" width="10.83203125" customWidth="1"/>
+    <col min="4" max="4" width="33.1640625" customWidth="1"/>
+    <col min="6" max="6" width="46" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="53" t="s">
-        <v>125</v>
+    <row r="1" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A1" s="47" t="s">
+        <v>116</v>
+      </c>
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+    </row>
+    <row r="2" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A2" s="44" t="s">
+        <v>117</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="54"/>
+        <v>118</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A3" s="45"/>
       <c r="F3" s="1"/>
     </row>
-    <row r="4">
+    <row r="4" spans="1:10" ht="15.75" customHeight="1">
       <c r="F4" s="3"/>
     </row>
-    <row r="5">
+    <row r="5" spans="1:10" ht="15.75" customHeight="1">
       <c r="F5" s="3"/>
     </row>
-    <row r="8">
-      <c r="F8" s="23" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="C9" s="8"/>
-    </row>
-    <row r="10">
-      <c r="F10" s="5" t="s">
+    <row r="8" spans="1:10" ht="15.75" customHeight="1">
+      <c r="F8" s="16" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="15.75" customHeight="1">
+      <c r="C9" s="50"/>
+      <c r="D9" s="48"/>
+      <c r="E9" s="48"/>
+      <c r="F9" s="48"/>
+    </row>
+    <row r="10" spans="1:10" ht="15.75" customHeight="1">
+      <c r="F10" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="8"/>
-      <c r="F11" s="6" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="G13" s="6"/>
-      <c r="H13" s="6"/>
-      <c r="I13" s="6"/>
-      <c r="J13" s="6"/>
-    </row>
-    <row r="14">
-      <c r="F14" s="6"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
-      <c r="I14" s="6"/>
-      <c r="J14" s="6"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="6"/>
-      <c r="F15" s="6"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="6"/>
-      <c r="I15" s="6"/>
-      <c r="J15" s="6"/>
-    </row>
-    <row r="16">
-      <c r="F16" s="6"/>
-      <c r="G16" s="6"/>
-      <c r="H16" s="6"/>
-      <c r="I16" s="6"/>
-      <c r="J16" s="6"/>
-    </row>
-    <row r="17">
-      <c r="F17" s="6"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="6"/>
-      <c r="I17" s="6"/>
-      <c r="J17" s="6"/>
-    </row>
-    <row r="18">
-      <c r="F18" s="6"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="6"/>
-      <c r="I18" s="6"/>
-      <c r="J18" s="6"/>
-    </row>
-    <row r="19">
-      <c r="F19" s="6"/>
-      <c r="G19" s="6"/>
-      <c r="H19" s="6"/>
-      <c r="I19" s="6"/>
-      <c r="J19" s="6"/>
-    </row>
-    <row r="20">
-      <c r="F20" s="6"/>
-      <c r="G20" s="6"/>
-      <c r="H20" s="6"/>
-      <c r="I20" s="6"/>
-      <c r="J20" s="6"/>
-    </row>
-    <row r="21">
-      <c r="F21" s="6"/>
-      <c r="G21" s="6"/>
-      <c r="H21" s="6"/>
-      <c r="I21" s="6"/>
-      <c r="J21" s="6"/>
-    </row>
-    <row r="22">
-      <c r="F22" s="6"/>
-      <c r="G22" s="6"/>
-      <c r="H22" s="6"/>
-      <c r="I22" s="6"/>
-      <c r="J22" s="6"/>
-    </row>
-    <row r="23">
-      <c r="F23" s="6"/>
-      <c r="G23" s="6"/>
-      <c r="H23" s="6"/>
-      <c r="I23" s="6"/>
-      <c r="J23" s="6"/>
+    <row r="11" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A11" s="50"/>
+      <c r="B11" s="48"/>
+      <c r="C11" s="48"/>
+      <c r="D11" s="48"/>
+      <c r="F11" s="5" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="15.75" customHeight="1">
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="5"/>
+    </row>
+    <row r="14" spans="1:10" ht="15.75" customHeight="1">
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="5"/>
+    </row>
+    <row r="15" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="5"/>
+    </row>
+    <row r="16" spans="1:10" ht="15.75" customHeight="1">
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="5"/>
+    </row>
+    <row r="17" spans="6:10" ht="15.75" customHeight="1">
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="5"/>
+      <c r="J17" s="5"/>
+    </row>
+    <row r="18" spans="6:10" ht="15.75" customHeight="1">
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
+      <c r="J18" s="5"/>
+    </row>
+    <row r="19" spans="6:10" ht="15.75" customHeight="1">
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="5"/>
+      <c r="J19" s="5"/>
+    </row>
+    <row r="20" spans="6:10" ht="15.75" customHeight="1">
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="5"/>
+      <c r="J20" s="5"/>
+    </row>
+    <row r="21" spans="6:10" ht="15.75" customHeight="1">
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
+      <c r="I21" s="5"/>
+      <c r="J21" s="5"/>
+    </row>
+    <row r="22" spans="6:10" ht="15.75" customHeight="1">
+      <c r="F22" s="5"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5"/>
+      <c r="I22" s="5"/>
+      <c r="J22" s="5"/>
+    </row>
+    <row r="23" spans="6:10" ht="15.75" customHeight="1">
+      <c r="F23" s="5"/>
+      <c r="G23" s="5"/>
+      <c r="H23" s="5"/>
+      <c r="I23" s="5"/>
+      <c r="J23" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -4685,176 +5820,186 @@
     <mergeCell ref="A11:D11"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink r:id="rId1" ref="F8"/>
+    <hyperlink ref="F8" r:id="rId1" xr:uid="{00000000-0004-0000-0D00-000000000000}"/>
   </hyperlinks>
-  <drawing r:id="rId2"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:J23"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="18.88"/>
-    <col customWidth="1" min="4" max="4" width="33.13"/>
-    <col customWidth="1" min="6" max="6" width="46.0"/>
-    <col customWidth="1" min="7" max="7" width="10.5"/>
-    <col customWidth="1" min="8" max="9" width="25.5"/>
+    <col min="1" max="1" width="18.83203125" customWidth="1"/>
+    <col min="4" max="4" width="33.1640625" customWidth="1"/>
+    <col min="6" max="6" width="46" customWidth="1"/>
+    <col min="7" max="7" width="10.5" customWidth="1"/>
+    <col min="8" max="9" width="25.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="55" t="s">
-        <v>130</v>
+    <row r="1" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A1" s="47" t="s">
+        <v>121</v>
+      </c>
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+    </row>
+    <row r="2" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A2" s="46" t="s">
+        <v>122</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="54"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="34" t="s">
-        <v>132</v>
-      </c>
-      <c r="B4" s="34" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A3" s="45"/>
+    </row>
+    <row r="4" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A4" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="B4" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="34" t="s">
+      <c r="C4" s="27" t="s">
         <v>18</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="35" t="s">
-        <v>133</v>
-      </c>
-      <c r="B5" s="36">
-        <v>134300.0</v>
-      </c>
-      <c r="C5" s="36">
-        <v>64700.0</v>
-      </c>
-      <c r="F5" s="23" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="35" t="s">
-        <v>135</v>
-      </c>
-      <c r="B6" s="36">
-        <v>57000.0</v>
-      </c>
-      <c r="C6" s="36">
-        <v>51760.0</v>
+    <row r="5" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A5" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="B5" s="29">
+        <v>134300</v>
+      </c>
+      <c r="C5" s="29">
+        <v>64700</v>
+      </c>
+      <c r="F5" s="56" t="s">
+        <v>126</v>
+      </c>
+      <c r="G5" s="48"/>
+      <c r="H5" s="48"/>
+      <c r="I5" s="48"/>
+    </row>
+    <row r="6" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A6" s="28" t="s">
+        <v>127</v>
+      </c>
+      <c r="B6" s="29">
+        <v>57000</v>
+      </c>
+      <c r="C6" s="29">
+        <v>51760</v>
       </c>
       <c r="F6" s="3"/>
     </row>
-    <row r="7">
-      <c r="F7" s="5" t="s">
+    <row r="7" spans="1:10" ht="15.75" customHeight="1">
+      <c r="F7" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8">
-      <c r="F8" s="6" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="8"/>
-    </row>
-    <row r="12">
-      <c r="G12" s="56"/>
-      <c r="H12" s="56"/>
-      <c r="I12" s="56"/>
-    </row>
-    <row r="13">
-      <c r="G13" s="56"/>
-      <c r="H13" s="56"/>
-      <c r="I13" s="56"/>
-      <c r="J13" s="6"/>
-    </row>
-    <row r="14">
-      <c r="F14" s="6"/>
-      <c r="G14" s="56"/>
-      <c r="H14" s="56"/>
-      <c r="I14" s="56"/>
-      <c r="J14" s="6"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="6"/>
-      <c r="F15" s="6"/>
-      <c r="G15" s="56"/>
-      <c r="H15" s="56"/>
-      <c r="I15" s="56"/>
-      <c r="J15" s="6"/>
-    </row>
-    <row r="16">
-      <c r="F16" s="6"/>
-      <c r="G16" s="56"/>
-      <c r="H16" s="56"/>
-      <c r="I16" s="56"/>
-      <c r="J16" s="6"/>
-    </row>
-    <row r="17">
-      <c r="F17" s="6"/>
-      <c r="G17" s="56"/>
-      <c r="H17" s="56"/>
-      <c r="I17" s="56"/>
-      <c r="J17" s="6"/>
-    </row>
-    <row r="18">
-      <c r="F18" s="6"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="6"/>
-      <c r="I18" s="6"/>
-      <c r="J18" s="6"/>
-    </row>
-    <row r="19">
-      <c r="F19" s="6"/>
-      <c r="G19" s="6"/>
-      <c r="H19" s="6"/>
-      <c r="I19" s="6"/>
-      <c r="J19" s="6"/>
-    </row>
-    <row r="20">
-      <c r="F20" s="6"/>
-      <c r="G20" s="6"/>
-      <c r="H20" s="6"/>
-      <c r="I20" s="6"/>
-      <c r="J20" s="6"/>
-    </row>
-    <row r="21">
-      <c r="F21" s="6"/>
-      <c r="G21" s="6"/>
-      <c r="H21" s="6"/>
-      <c r="I21" s="6"/>
-      <c r="J21" s="6"/>
-    </row>
-    <row r="22">
-      <c r="F22" s="6"/>
-      <c r="G22" s="6"/>
-      <c r="H22" s="6"/>
-      <c r="I22" s="6"/>
-      <c r="J22" s="6"/>
-    </row>
-    <row r="23">
-      <c r="F23" s="6"/>
-      <c r="G23" s="6"/>
-      <c r="H23" s="6"/>
-      <c r="I23" s="6"/>
-      <c r="J23" s="6"/>
+    <row r="8" spans="1:10" ht="15.75" customHeight="1">
+      <c r="F8" s="5" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A11" s="50"/>
+      <c r="B11" s="48"/>
+      <c r="C11" s="48"/>
+      <c r="D11" s="48"/>
+    </row>
+    <row r="12" spans="1:10" ht="15.75" customHeight="1">
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+    </row>
+    <row r="13" spans="1:10" ht="15.75" customHeight="1">
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="5"/>
+    </row>
+    <row r="14" spans="1:10" ht="15.75" customHeight="1">
+      <c r="F14" s="5"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="5"/>
+    </row>
+    <row r="15" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="5"/>
+    </row>
+    <row r="16" spans="1:10" ht="15.75" customHeight="1">
+      <c r="F16" s="5"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="5"/>
+    </row>
+    <row r="17" spans="6:10" ht="15.75" customHeight="1">
+      <c r="F17" s="5"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="5"/>
+    </row>
+    <row r="18" spans="6:10" ht="15.75" customHeight="1">
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
+      <c r="J18" s="5"/>
+    </row>
+    <row r="19" spans="6:10" ht="15.75" customHeight="1">
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="5"/>
+      <c r="J19" s="5"/>
+    </row>
+    <row r="20" spans="6:10" ht="15.75" customHeight="1">
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="5"/>
+      <c r="J20" s="5"/>
+    </row>
+    <row r="21" spans="6:10" ht="15.75" customHeight="1">
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
+      <c r="I21" s="5"/>
+      <c r="J21" s="5"/>
+    </row>
+    <row r="22" spans="6:10" ht="15.75" customHeight="1">
+      <c r="F22" s="5"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5"/>
+      <c r="I22" s="5"/>
+      <c r="J22" s="5"/>
+    </row>
+    <row r="23" spans="6:10" ht="15.75" customHeight="1">
+      <c r="F23" s="5"/>
+      <c r="G23" s="5"/>
+      <c r="H23" s="5"/>
+      <c r="I23" s="5"/>
+      <c r="J23" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -4863,35 +6008,40 @@
     <mergeCell ref="A11:D11"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink r:id="rId1" ref="F5"/>
+    <hyperlink ref="F5" r:id="rId1" xr:uid="{00000000-0004-0000-0E00-000000000000}"/>
   </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:J23"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="10.88"/>
-    <col customWidth="1" min="4" max="4" width="33.13"/>
-    <col customWidth="1" min="6" max="6" width="45.88"/>
+    <col min="1" max="1" width="10.83203125" customWidth="1"/>
+    <col min="4" max="4" width="33.1640625" customWidth="1"/>
+    <col min="6" max="6" width="45.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A1" s="47" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2">
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+    </row>
+    <row r="2" spans="1:10" ht="15.75" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:10" ht="15.75" customHeight="1">
       <c r="A3" s="3"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -4899,33 +6049,33 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:10" ht="15.75" customHeight="1">
       <c r="A4" s="3"/>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
       <c r="F4" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:10" ht="15.75" customHeight="1">
       <c r="A5" s="3"/>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
+      <c r="B5" s="6"/>
+      <c r="C5" s="6"/>
       <c r="F5" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:10" ht="15.75" customHeight="1">
       <c r="A6" s="3"/>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-    </row>
-    <row r="7">
+      <c r="B6" s="6"/>
+      <c r="C6" s="6"/>
+    </row>
+    <row r="7" spans="1:10" ht="15.75" customHeight="1">
       <c r="A7" s="3"/>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-    </row>
-    <row r="8">
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+    </row>
+    <row r="8" spans="1:10" ht="15.75" customHeight="1">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -4933,98 +6083,104 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9">
-      <c r="F9" s="8" t="s">
+    <row r="9" spans="1:10" ht="15.75" customHeight="1">
+      <c r="F9" s="50" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="10">
-      <c r="F10" s="8"/>
-    </row>
-    <row r="12">
-      <c r="F12" s="5" t="s">
+      <c r="G9" s="48"/>
+      <c r="H9" s="48"/>
+      <c r="I9" s="48"/>
+    </row>
+    <row r="10" spans="1:10" ht="15.75" customHeight="1">
+      <c r="F10" s="50"/>
+      <c r="G10" s="48"/>
+      <c r="H10" s="48"/>
+      <c r="I10" s="48"/>
+    </row>
+    <row r="12" spans="1:10" ht="15.75" customHeight="1">
+      <c r="F12" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="13">
-      <c r="F13" s="6" t="s">
+    <row r="13" spans="1:10" ht="15.75" customHeight="1">
+      <c r="F13" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6"/>
-      <c r="I13" s="6"/>
-      <c r="J13" s="6"/>
-    </row>
-    <row r="14">
-      <c r="F14" s="6"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
-      <c r="I14" s="6"/>
-      <c r="J14" s="6"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="6"/>
-      <c r="F15" s="6"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="6"/>
-      <c r="I15" s="6"/>
-      <c r="J15" s="6"/>
-    </row>
-    <row r="16">
-      <c r="F16" s="6"/>
-      <c r="G16" s="6"/>
-      <c r="H16" s="6"/>
-      <c r="I16" s="6"/>
-      <c r="J16" s="6"/>
-    </row>
-    <row r="17">
-      <c r="F17" s="6"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="6"/>
-      <c r="I17" s="6"/>
-      <c r="J17" s="6"/>
-    </row>
-    <row r="18">
-      <c r="F18" s="6"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="6"/>
-      <c r="I18" s="6"/>
-      <c r="J18" s="6"/>
-    </row>
-    <row r="19">
-      <c r="F19" s="6"/>
-      <c r="G19" s="6"/>
-      <c r="H19" s="6"/>
-      <c r="I19" s="6"/>
-      <c r="J19" s="6"/>
-    </row>
-    <row r="20">
-      <c r="F20" s="6"/>
-      <c r="G20" s="6"/>
-      <c r="H20" s="6"/>
-      <c r="I20" s="6"/>
-      <c r="J20" s="6"/>
-    </row>
-    <row r="21">
-      <c r="F21" s="6"/>
-      <c r="G21" s="6"/>
-      <c r="H21" s="6"/>
-      <c r="I21" s="6"/>
-      <c r="J21" s="6"/>
-    </row>
-    <row r="22">
-      <c r="F22" s="6"/>
-      <c r="G22" s="6"/>
-      <c r="H22" s="6"/>
-      <c r="I22" s="6"/>
-      <c r="J22" s="6"/>
-    </row>
-    <row r="23">
-      <c r="F23" s="6"/>
-      <c r="G23" s="6"/>
-      <c r="H23" s="6"/>
-      <c r="I23" s="6"/>
-      <c r="J23" s="6"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="5"/>
+    </row>
+    <row r="14" spans="1:10" ht="15.75" customHeight="1">
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="5"/>
+    </row>
+    <row r="15" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="5"/>
+    </row>
+    <row r="16" spans="1:10" ht="15.75" customHeight="1">
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="5"/>
+    </row>
+    <row r="17" spans="6:10" ht="15.75" customHeight="1">
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="5"/>
+      <c r="J17" s="5"/>
+    </row>
+    <row r="18" spans="6:10" ht="15.75" customHeight="1">
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
+      <c r="J18" s="5"/>
+    </row>
+    <row r="19" spans="6:10" ht="15.75" customHeight="1">
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="5"/>
+      <c r="J19" s="5"/>
+    </row>
+    <row r="20" spans="6:10" ht="15.75" customHeight="1">
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="5"/>
+      <c r="J20" s="5"/>
+    </row>
+    <row r="21" spans="6:10" ht="15.75" customHeight="1">
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
+      <c r="I21" s="5"/>
+      <c r="J21" s="5"/>
+    </row>
+    <row r="22" spans="6:10" ht="15.75" customHeight="1">
+      <c r="F22" s="5"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5"/>
+      <c r="I22" s="5"/>
+      <c r="J22" s="5"/>
+    </row>
+    <row r="23" spans="6:10" ht="15.75" customHeight="1">
+      <c r="F23" s="5"/>
+      <c r="G23" s="5"/>
+      <c r="H23" s="5"/>
+      <c r="I23" s="5"/>
+      <c r="J23" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -5032,82 +6188,86 @@
     <mergeCell ref="F9:I9"/>
     <mergeCell ref="F10:I10"/>
   </mergeCells>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:K15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="4" max="4" width="49.25"/>
-    <col customWidth="1" min="5" max="5" width="43.13"/>
-    <col customWidth="1" min="6" max="6" width="35.5"/>
+    <col min="4" max="4" width="49.1640625" customWidth="1"/>
+    <col min="5" max="5" width="43.1640625" customWidth="1"/>
+    <col min="6" max="6" width="35.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:11">
+      <c r="A1" s="51" t="s">
         <v>15</v>
       </c>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="11" t="s">
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
+      <c r="I1" s="7"/>
+    </row>
+    <row r="4" spans="1:11" ht="15.75" customHeight="1">
+      <c r="A4" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="8" t="s">
         <v>18</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="12">
-        <v>2021.0</v>
-      </c>
-      <c r="B5" s="12">
+    <row r="5" spans="1:11" ht="15.75" customHeight="1">
+      <c r="A5" s="9">
+        <v>2021</v>
+      </c>
+      <c r="B5" s="9">
         <v>92.012</v>
       </c>
-      <c r="C5" s="12">
+      <c r="C5" s="9">
         <v>92.4</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="12">
-        <v>2022.0</v>
-      </c>
-      <c r="B6" s="12">
+    <row r="6" spans="1:11" ht="15.75" customHeight="1">
+      <c r="A6" s="9">
+        <v>2022</v>
+      </c>
+      <c r="B6" s="9">
         <v>90.991</v>
       </c>
-      <c r="C6" s="12">
+      <c r="C6" s="9">
         <v>91.4</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="12">
-        <v>2023.0</v>
-      </c>
-      <c r="B7" s="12">
-        <v>91.104</v>
-      </c>
-      <c r="C7" s="12">
+    <row r="7" spans="1:11" ht="15.75" customHeight="1">
+      <c r="A7" s="9">
+        <v>2023</v>
+      </c>
+      <c r="B7" s="9">
+        <v>91.103999999999999</v>
+      </c>
+      <c r="C7" s="9">
         <v>91.4</v>
       </c>
       <c r="E7" s="2"/>
@@ -5115,225 +6275,246 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="12">
-        <v>2024.0</v>
-      </c>
-      <c r="B8" s="12">
-        <v>90.817</v>
-      </c>
-      <c r="C8" s="12">
+    <row r="8" spans="1:11" ht="15.75" customHeight="1">
+      <c r="A8" s="9">
+        <v>2024</v>
+      </c>
+      <c r="B8" s="9">
+        <v>90.816999999999993</v>
+      </c>
+      <c r="C8" s="9">
         <v>87.8</v>
       </c>
-      <c r="D8" s="6"/>
+      <c r="D8" s="5"/>
       <c r="E8" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="12">
-        <v>2025.0</v>
-      </c>
-      <c r="B9" s="12" t="s">
+    <row r="9" spans="1:11" ht="15.75" customHeight="1">
+      <c r="A9" s="9">
+        <v>2025</v>
+      </c>
+      <c r="B9" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="C9" s="9" t="s">
         <v>21</v>
       </c>
       <c r="D9" s="2"/>
-      <c r="E9" s="13" t="s">
+      <c r="E9" s="52" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="10">
+      <c r="F9" s="48"/>
+      <c r="G9" s="48"/>
+    </row>
+    <row r="10" spans="1:11" ht="15.75" customHeight="1">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="D10" s="2"/>
-      <c r="E10" s="14" t="s">
+      <c r="E10" s="53" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="15"/>
-      <c r="E11" s="6" t="s">
+      <c r="F10" s="48"/>
+      <c r="G10" s="48"/>
+    </row>
+    <row r="11" spans="1:11" ht="15.75" customHeight="1">
+      <c r="A11" s="54"/>
+      <c r="B11" s="48"/>
+      <c r="C11" s="48"/>
+      <c r="E11" s="5" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="16"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="17"/>
-    </row>
-    <row r="14">
+    <row r="12" spans="1:11" ht="15.75" customHeight="1">
+      <c r="A12" s="54"/>
+      <c r="B12" s="48"/>
+      <c r="C12" s="48"/>
+    </row>
+    <row r="13" spans="1:11" ht="15.75" customHeight="1">
+      <c r="A13" s="55"/>
+      <c r="B13" s="48"/>
+      <c r="C13" s="48"/>
+    </row>
+    <row r="14" spans="1:11" ht="15.75" customHeight="1">
       <c r="E14" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="15">
-      <c r="E15" s="6" t="s">
+    <row r="15" spans="1:11" ht="15.75" customHeight="1">
+      <c r="E15" s="5" t="s">
         <v>25</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="A13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="E9:G9"/>
     <mergeCell ref="E10:G10"/>
     <mergeCell ref="A11:C11"/>
     <mergeCell ref="A12:C12"/>
-    <mergeCell ref="A13:C13"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink r:id="rId1" ref="E9"/>
-    <hyperlink r:id="rId2" ref="E10"/>
+    <hyperlink ref="E9" r:id="rId1" xr:uid="{00000000-0004-0000-0200-000000000000}"/>
+    <hyperlink ref="E10" r:id="rId2" xr:uid="{00000000-0004-0000-0200-000001000000}"/>
   </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:K17"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="4" max="4" width="49.25"/>
-    <col customWidth="1" min="5" max="5" width="43.13"/>
-    <col customWidth="1" min="6" max="6" width="87.25"/>
+    <col min="4" max="4" width="49.1640625" customWidth="1"/>
+    <col min="5" max="5" width="43.1640625" customWidth="1"/>
+    <col min="6" max="6" width="87.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:11">
       <c r="A1" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="9" t="s">
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
+      <c r="I1" s="7"/>
+    </row>
+    <row r="3" spans="1:11" ht="15.75" customHeight="1">
+      <c r="A3" s="51" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="18" t="s">
+      <c r="B3" s="48"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="48"/>
+    </row>
+    <row r="4" spans="1:11" ht="15.75" customHeight="1">
+      <c r="A4" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="18" t="s">
+      <c r="B4" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="18" t="s">
+      <c r="C4" s="11" t="s">
         <v>18</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="19">
-        <v>2021.0</v>
-      </c>
-      <c r="B5" s="20">
+    <row r="5" spans="1:11" ht="15.75" customHeight="1">
+      <c r="A5" s="12">
+        <v>2021</v>
+      </c>
+      <c r="B5" s="13">
         <v>72.8</v>
       </c>
-      <c r="C5" s="21">
-        <v>67.0</v>
+      <c r="C5" s="14">
+        <v>67</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="19">
-        <v>2022.0</v>
-      </c>
-      <c r="B6" s="21">
-        <v>70.6</v>
-      </c>
-      <c r="C6" s="21">
+    <row r="6" spans="1:11" ht="15.75" customHeight="1">
+      <c r="A6" s="12">
+        <v>2022</v>
+      </c>
+      <c r="B6" s="14">
+        <v>70.599999999999994</v>
+      </c>
+      <c r="C6" s="14">
         <v>68.5</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="19">
-        <v>2023.0</v>
-      </c>
-      <c r="B7" s="21">
+    <row r="7" spans="1:11" ht="15.75" customHeight="1">
+      <c r="A7" s="12">
+        <v>2023</v>
+      </c>
+      <c r="B7" s="14">
         <v>68.7</v>
       </c>
-      <c r="C7" s="22">
-        <v>68.0</v>
+      <c r="C7" s="15">
+        <v>68</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="19">
-        <v>2024.0</v>
-      </c>
-      <c r="B8" s="21">
+    <row r="8" spans="1:11" ht="15.75" customHeight="1">
+      <c r="A8" s="12">
+        <v>2024</v>
+      </c>
+      <c r="B8" s="14">
         <v>70.5</v>
       </c>
-      <c r="C8" s="22">
+      <c r="C8" s="15">
         <v>66.8</v>
       </c>
-      <c r="D8" s="6"/>
+      <c r="D8" s="5"/>
       <c r="E8" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="19">
-        <v>2025.0</v>
-      </c>
-      <c r="B9" s="21">
+    <row r="9" spans="1:11" ht="15.75" customHeight="1">
+      <c r="A9" s="12">
+        <v>2025</v>
+      </c>
+      <c r="B9" s="14">
         <v>68.3</v>
       </c>
-      <c r="C9" s="21">
+      <c r="C9" s="14">
         <v>63.8</v>
       </c>
       <c r="D9" s="2"/>
-      <c r="E9" s="23" t="s">
+      <c r="E9" s="16" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:11" ht="15.75" customHeight="1">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="D10" s="2"/>
-      <c r="E10" s="23" t="s">
+      <c r="E10" s="16" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="15"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="16"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="17"/>
-    </row>
-    <row r="15">
+    <row r="11" spans="1:11" ht="15.75" customHeight="1">
+      <c r="A11" s="54"/>
+      <c r="B11" s="48"/>
+      <c r="C11" s="48"/>
+    </row>
+    <row r="12" spans="1:11" ht="15.75" customHeight="1">
+      <c r="A12" s="54"/>
+      <c r="B12" s="48"/>
+      <c r="C12" s="48"/>
+    </row>
+    <row r="13" spans="1:11" ht="15.75" customHeight="1">
+      <c r="A13" s="55"/>
+      <c r="B13" s="48"/>
+      <c r="C13" s="48"/>
+    </row>
+    <row r="15" spans="1:11" ht="15.75" customHeight="1">
       <c r="E15" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="16">
-      <c r="E16" s="24" t="s">
+    <row r="16" spans="1:11" ht="15.75" customHeight="1">
+      <c r="E16" s="17" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="17">
-      <c r="E17" s="25"/>
+    <row r="17" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E17" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -5343,164 +6524,172 @@
     <mergeCell ref="A13:C13"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink r:id="rId1" ref="E9"/>
-    <hyperlink r:id="rId2" ref="E10"/>
+    <hyperlink ref="E9" r:id="rId1" xr:uid="{00000000-0004-0000-0300-000000000000}"/>
+    <hyperlink ref="E10" r:id="rId2" xr:uid="{00000000-0004-0000-0300-000001000000}"/>
   </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId3"/>
   <tableParts count="1">
-    <tablePart r:id="rId5"/>
+    <tablePart r:id="rId4"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:J23"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="43.0"/>
-    <col customWidth="1" min="4" max="4" width="33.13"/>
-    <col customWidth="1" min="6" max="6" width="46.0"/>
-    <col customWidth="1" min="9" max="9" width="35.0"/>
+    <col min="1" max="1" width="43" customWidth="1"/>
+    <col min="4" max="4" width="33.1640625" customWidth="1"/>
+    <col min="6" max="6" width="46" customWidth="1"/>
+    <col min="9" max="9" width="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A1" s="47" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="26" t="s">
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+    </row>
+    <row r="2" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A2" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="26"/>
-      <c r="I2" s="26"/>
-    </row>
-    <row r="4">
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="19"/>
+      <c r="I2" s="19"/>
+    </row>
+    <row r="4" spans="1:10" ht="15.75" customHeight="1">
       <c r="D4" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:10" ht="15.75" customHeight="1">
       <c r="D5" s="3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:10" ht="15.75" customHeight="1">
       <c r="D6" s="3" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:10" ht="15.75" customHeight="1">
       <c r="A9" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="23" t="s">
+    <row r="10" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A10" s="56" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="27" t="s">
+      <c r="B10" s="48"/>
+      <c r="C10" s="48"/>
+      <c r="D10" s="48"/>
+    </row>
+    <row r="11" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A11" s="20" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="27" t="s">
+    <row r="12" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A12" s="20" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="5" t="s">
+    <row r="13" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A13" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="J13" s="6"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="6" t="s">
+      <c r="J13" s="5"/>
+    </row>
+    <row r="14" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A14" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="6"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
-      <c r="F14" s="6"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
-      <c r="I14" s="6"/>
-      <c r="J14" s="6"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="6"/>
-      <c r="F15" s="6"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="6"/>
-      <c r="I15" s="6"/>
-      <c r="J15" s="6"/>
-    </row>
-    <row r="16">
-      <c r="F16" s="6"/>
-      <c r="G16" s="6"/>
-      <c r="H16" s="6"/>
-      <c r="I16" s="6"/>
-      <c r="J16" s="6"/>
-    </row>
-    <row r="17">
-      <c r="F17" s="6"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="6"/>
-      <c r="I17" s="6"/>
-      <c r="J17" s="6"/>
-    </row>
-    <row r="18">
-      <c r="F18" s="6"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="6"/>
-      <c r="I18" s="6"/>
-      <c r="J18" s="6"/>
-    </row>
-    <row r="19">
-      <c r="F19" s="6"/>
-      <c r="G19" s="6"/>
-      <c r="H19" s="6"/>
-      <c r="I19" s="6"/>
-      <c r="J19" s="6"/>
-    </row>
-    <row r="20">
-      <c r="F20" s="6"/>
-      <c r="G20" s="6"/>
-      <c r="H20" s="6"/>
-      <c r="I20" s="6"/>
-      <c r="J20" s="6"/>
-    </row>
-    <row r="21">
-      <c r="F21" s="6"/>
-      <c r="G21" s="6"/>
-      <c r="H21" s="6"/>
-      <c r="I21" s="6"/>
-      <c r="J21" s="6"/>
-    </row>
-    <row r="22">
-      <c r="F22" s="6"/>
-      <c r="G22" s="6"/>
-      <c r="H22" s="6"/>
-      <c r="I22" s="6"/>
-      <c r="J22" s="6"/>
-    </row>
-    <row r="23">
-      <c r="F23" s="6"/>
-      <c r="G23" s="6"/>
-      <c r="H23" s="6"/>
-      <c r="I23" s="6"/>
-      <c r="J23" s="6"/>
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="5"/>
+    </row>
+    <row r="15" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="5"/>
+    </row>
+    <row r="16" spans="1:10" ht="15.75" customHeight="1">
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="5"/>
+    </row>
+    <row r="17" spans="6:10" ht="15.75" customHeight="1">
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="5"/>
+      <c r="J17" s="5"/>
+    </row>
+    <row r="18" spans="6:10" ht="15.75" customHeight="1">
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
+      <c r="J18" s="5"/>
+    </row>
+    <row r="19" spans="6:10" ht="15.75" customHeight="1">
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="5"/>
+      <c r="J19" s="5"/>
+    </row>
+    <row r="20" spans="6:10" ht="15.75" customHeight="1">
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="5"/>
+      <c r="J20" s="5"/>
+    </row>
+    <row r="21" spans="6:10" ht="15.75" customHeight="1">
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
+      <c r="I21" s="5"/>
+      <c r="J21" s="5"/>
+    </row>
+    <row r="22" spans="6:10" ht="15.75" customHeight="1">
+      <c r="F22" s="5"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5"/>
+      <c r="I22" s="5"/>
+      <c r="J22" s="5"/>
+    </row>
+    <row r="23" spans="6:10" ht="15.75" customHeight="1">
+      <c r="F23" s="5"/>
+      <c r="G23" s="5"/>
+      <c r="H23" s="5"/>
+      <c r="I23" s="5"/>
+      <c r="J23" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -5508,393 +6697,399 @@
     <mergeCell ref="A10:D10"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink r:id="rId1" ref="A10"/>
-    <hyperlink r:id="rId2" ref="A11"/>
-    <hyperlink r:id="rId3" ref="A12"/>
+    <hyperlink ref="A10" r:id="rId1" xr:uid="{00000000-0004-0000-0400-000000000000}"/>
+    <hyperlink ref="A11" r:id="rId2" xr:uid="{00000000-0004-0000-0400-000001000000}"/>
+    <hyperlink ref="A12" r:id="rId3" xr:uid="{00000000-0004-0000-0400-000002000000}"/>
   </hyperlinks>
-  <drawing r:id="rId4"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:J23"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="60.38"/>
-    <col customWidth="1" min="4" max="4" width="33.13"/>
-    <col customWidth="1" min="6" max="6" width="46.0"/>
-    <col customWidth="1" min="8" max="8" width="4.5"/>
+    <col min="1" max="1" width="60.33203125" customWidth="1"/>
+    <col min="4" max="4" width="33.1640625" customWidth="1"/>
+    <col min="6" max="6" width="46" customWidth="1"/>
+    <col min="8" max="8" width="4.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="28" t="s">
+    <row r="1" spans="1:10">
+      <c r="A1" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="6" t="s">
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="24"/>
+      <c r="J1" s="24"/>
+    </row>
+    <row r="2" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A2" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-    </row>
-    <row r="3">
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="5"/>
+    </row>
+    <row r="3" spans="1:10" ht="15.75" customHeight="1">
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="D3" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:10" ht="15.75" customHeight="1">
       <c r="A4" s="3"/>
-      <c r="B4" s="32"/>
-      <c r="C4" s="32"/>
+      <c r="B4" s="25"/>
+      <c r="C4" s="25"/>
       <c r="D4" s="3" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:10" ht="15.75" customHeight="1">
       <c r="A5" s="3"/>
-      <c r="B5" s="32"/>
-      <c r="C5" s="32"/>
+      <c r="B5" s="25"/>
+      <c r="C5" s="25"/>
       <c r="D5" s="3" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:10" ht="15.75" customHeight="1">
       <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="23" t="s">
+    <row r="7" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A7" s="56" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="33" t="s">
+      <c r="B7" s="48"/>
+      <c r="C7" s="48"/>
+      <c r="D7" s="48"/>
+    </row>
+    <row r="8" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A8" s="26" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="27" t="s">
+    <row r="9" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A9" s="20" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="5" t="s">
+    <row r="10" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A10" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="6" t="s">
+    <row r="11" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A11" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="B11" s="6"/>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
-    </row>
-    <row r="13">
-      <c r="J13" s="6"/>
-    </row>
-    <row r="14">
-      <c r="F14" s="6"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
-      <c r="I14" s="6"/>
-      <c r="J14" s="6"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="6"/>
-      <c r="F15" s="6"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="6"/>
-      <c r="I15" s="6"/>
-      <c r="J15" s="6"/>
-    </row>
-    <row r="16">
-      <c r="F16" s="6"/>
-      <c r="G16" s="6"/>
-      <c r="H16" s="6"/>
-      <c r="I16" s="6"/>
-      <c r="J16" s="6"/>
-    </row>
-    <row r="17">
-      <c r="F17" s="6"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="6"/>
-      <c r="I17" s="6"/>
-      <c r="J17" s="6"/>
-    </row>
-    <row r="18">
-      <c r="F18" s="6"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="6"/>
-      <c r="I18" s="6"/>
-      <c r="J18" s="6"/>
-    </row>
-    <row r="19">
-      <c r="F19" s="6"/>
-      <c r="G19" s="6"/>
-      <c r="H19" s="6"/>
-      <c r="I19" s="6"/>
-      <c r="J19" s="6"/>
-    </row>
-    <row r="20">
-      <c r="F20" s="6"/>
-      <c r="G20" s="6"/>
-      <c r="H20" s="6"/>
-      <c r="I20" s="6"/>
-      <c r="J20" s="6"/>
-    </row>
-    <row r="21">
-      <c r="F21" s="6"/>
-      <c r="G21" s="6"/>
-      <c r="H21" s="6"/>
-      <c r="I21" s="6"/>
-      <c r="J21" s="6"/>
-    </row>
-    <row r="22">
-      <c r="F22" s="6"/>
-      <c r="G22" s="6"/>
-      <c r="H22" s="6"/>
-      <c r="I22" s="6"/>
-      <c r="J22" s="6"/>
-    </row>
-    <row r="23">
-      <c r="F23" s="6"/>
-      <c r="G23" s="6"/>
-      <c r="H23" s="6"/>
-      <c r="I23" s="6"/>
-      <c r="J23" s="6"/>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+    </row>
+    <row r="13" spans="1:10" ht="15.75" customHeight="1">
+      <c r="J13" s="5"/>
+    </row>
+    <row r="14" spans="1:10" ht="15.75" customHeight="1">
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="5"/>
+    </row>
+    <row r="15" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="5"/>
+    </row>
+    <row r="16" spans="1:10" ht="15.75" customHeight="1">
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="5"/>
+    </row>
+    <row r="17" spans="6:10" ht="15.75" customHeight="1">
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="5"/>
+      <c r="J17" s="5"/>
+    </row>
+    <row r="18" spans="6:10" ht="15.75" customHeight="1">
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
+      <c r="J18" s="5"/>
+    </row>
+    <row r="19" spans="6:10" ht="15.75" customHeight="1">
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="5"/>
+      <c r="J19" s="5"/>
+    </row>
+    <row r="20" spans="6:10" ht="15.75" customHeight="1">
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="5"/>
+      <c r="J20" s="5"/>
+    </row>
+    <row r="21" spans="6:10" ht="15.75" customHeight="1">
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
+      <c r="I21" s="5"/>
+      <c r="J21" s="5"/>
+    </row>
+    <row r="22" spans="6:10" ht="15.75" customHeight="1">
+      <c r="F22" s="5"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5"/>
+      <c r="I22" s="5"/>
+      <c r="J22" s="5"/>
+    </row>
+    <row r="23" spans="6:10" ht="15.75" customHeight="1">
+      <c r="F23" s="5"/>
+      <c r="G23" s="5"/>
+      <c r="H23" s="5"/>
+      <c r="I23" s="5"/>
+      <c r="J23" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A7:D7"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink r:id="rId1" ref="A7"/>
-    <hyperlink r:id="rId2" ref="A8"/>
-    <hyperlink r:id="rId3" ref="A9"/>
+    <hyperlink ref="A7" r:id="rId1" xr:uid="{00000000-0004-0000-0500-000000000000}"/>
+    <hyperlink ref="A8" r:id="rId2" xr:uid="{00000000-0004-0000-0500-000001000000}"/>
+    <hyperlink ref="A9" r:id="rId3" xr:uid="{00000000-0004-0000-0500-000002000000}"/>
   </hyperlinks>
-  <drawing r:id="rId4"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:J22"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="64.13"/>
-    <col customWidth="1" min="4" max="4" width="33.13"/>
-    <col customWidth="1" min="6" max="6" width="46.0"/>
-    <col customWidth="1" min="8" max="8" width="28.5"/>
+    <col min="1" max="1" width="64.1640625" customWidth="1"/>
+    <col min="4" max="4" width="33.1640625" customWidth="1"/>
+    <col min="6" max="6" width="46" customWidth="1"/>
+    <col min="8" max="8" width="28.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A1" s="47" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="6" t="s">
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+    </row>
+    <row r="2" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A2" s="5" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="34" t="s">
+    <row r="3" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A3" s="27" t="s">
         <v>49</v>
       </c>
-      <c r="B3" s="34" t="s">
+      <c r="B3" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="34" t="s">
+      <c r="C3" s="27" t="s">
         <v>18</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="H3" s="6"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="35">
-        <v>2020.0</v>
-      </c>
-      <c r="B4" s="36">
-        <v>72797.0</v>
-      </c>
-      <c r="C4" s="36">
-        <v>42000.0</v>
+      <c r="H3" s="5"/>
+    </row>
+    <row r="4" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A4" s="28">
+        <v>2020</v>
+      </c>
+      <c r="B4" s="29">
+        <v>72797</v>
+      </c>
+      <c r="C4" s="29">
+        <v>42000</v>
       </c>
       <c r="F4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G4" s="2"/>
+    </row>
+    <row r="5" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A5" s="28">
+        <v>2021</v>
+      </c>
+      <c r="B5" s="29">
+        <v>79791</v>
+      </c>
+      <c r="C5" s="29">
+        <v>44760</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="G5" s="2"/>
+    </row>
+    <row r="6" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A6" s="28">
+        <v>2022</v>
+      </c>
+      <c r="B6" s="29">
+        <v>79431</v>
+      </c>
+      <c r="C6" s="29">
+        <v>44566</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A7" s="28">
+        <v>2023</v>
+      </c>
+      <c r="B7" s="29">
+        <v>80825</v>
+      </c>
+      <c r="C7" s="29">
+        <v>45760</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="15.75" customHeight="1">
+      <c r="F8" s="56" t="s">
         <v>50</v>
       </c>
-      <c r="G4" s="2">
-        <v>5.0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="35">
-        <v>2021.0</v>
-      </c>
-      <c r="B5" s="36">
-        <v>79791.0</v>
-      </c>
-      <c r="C5" s="36">
-        <v>44760.0</v>
-      </c>
-      <c r="F5" s="3" t="s">
+      <c r="G8" s="48"/>
+      <c r="H8" s="48"/>
+      <c r="I8" s="48"/>
+    </row>
+    <row r="9" spans="1:10" ht="15.75" customHeight="1">
+      <c r="F9" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="G5" s="2">
-        <v>2.83</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="35">
-        <v>2022.0</v>
-      </c>
-      <c r="B6" s="36">
-        <v>79431.0</v>
-      </c>
-      <c r="C6" s="36">
-        <v>44566.0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="35">
-        <v>2023.0</v>
-      </c>
-      <c r="B7" s="36">
-        <v>80825.0</v>
-      </c>
-      <c r="C7" s="36">
-        <v>45760.0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="F8" s="23" t="s">
+    </row>
+    <row r="10" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A10" s="50"/>
+      <c r="B10" s="48"/>
+      <c r="C10" s="48"/>
+      <c r="D10" s="48"/>
+      <c r="H10" s="2"/>
+    </row>
+    <row r="11" spans="1:10" ht="15.75" customHeight="1">
+      <c r="F11" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H11" s="2"/>
+    </row>
+    <row r="12" spans="1:10" ht="15.75" customHeight="1">
+      <c r="F12" s="5" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="9">
-      <c r="F9" s="23" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="8"/>
-      <c r="H10" s="2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="F11" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="F12" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="G12" s="6"/>
-      <c r="H12" s="37"/>
-      <c r="I12" s="6"/>
-      <c r="J12" s="6"/>
-    </row>
-    <row r="13">
-      <c r="F13" s="6"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="38"/>
-      <c r="I13" s="6"/>
-      <c r="J13" s="6"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="6"/>
-      <c r="F14" s="6"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
-      <c r="I14" s="6"/>
-      <c r="J14" s="6"/>
-    </row>
-    <row r="15">
-      <c r="F15" s="6"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="6"/>
-      <c r="I15" s="6"/>
-      <c r="J15" s="6"/>
-    </row>
-    <row r="16">
-      <c r="F16" s="6"/>
-      <c r="G16" s="6"/>
-      <c r="H16" s="6"/>
-      <c r="I16" s="6"/>
-      <c r="J16" s="6"/>
-    </row>
-    <row r="17">
-      <c r="F17" s="6"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="6"/>
-      <c r="I17" s="6"/>
-      <c r="J17" s="6"/>
-    </row>
-    <row r="18">
-      <c r="F18" s="6"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="6"/>
-      <c r="I18" s="6"/>
-      <c r="J18" s="6"/>
-    </row>
-    <row r="19">
-      <c r="F19" s="6"/>
-      <c r="G19" s="6"/>
-      <c r="H19" s="6"/>
-      <c r="I19" s="6"/>
-      <c r="J19" s="6"/>
-    </row>
-    <row r="20">
-      <c r="F20" s="6"/>
-      <c r="G20" s="6"/>
-      <c r="H20" s="6"/>
-      <c r="I20" s="6"/>
-      <c r="J20" s="6"/>
-    </row>
-    <row r="21">
-      <c r="F21" s="6"/>
-      <c r="G21" s="6"/>
-      <c r="H21" s="6"/>
-      <c r="I21" s="6"/>
-      <c r="J21" s="6"/>
-    </row>
-    <row r="22">
-      <c r="F22" s="6"/>
-      <c r="G22" s="6"/>
-      <c r="H22" s="6"/>
-      <c r="I22" s="6"/>
-      <c r="J22" s="6"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="30"/>
+      <c r="I12" s="5"/>
+      <c r="J12" s="5"/>
+    </row>
+    <row r="13" spans="1:10" ht="15.75" customHeight="1">
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="30"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="5"/>
+    </row>
+    <row r="14" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="5"/>
+    </row>
+    <row r="15" spans="1:10" ht="15.75" customHeight="1">
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="5"/>
+    </row>
+    <row r="16" spans="1:10" ht="15.75" customHeight="1">
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="5"/>
+    </row>
+    <row r="17" spans="6:10" ht="15.75" customHeight="1">
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="5"/>
+      <c r="J17" s="5"/>
+    </row>
+    <row r="18" spans="6:10" ht="15.75" customHeight="1">
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
+      <c r="J18" s="5"/>
+    </row>
+    <row r="19" spans="6:10" ht="15.75" customHeight="1">
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="5"/>
+      <c r="J19" s="5"/>
+    </row>
+    <row r="20" spans="6:10" ht="15.75" customHeight="1">
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="5"/>
+      <c r="J20" s="5"/>
+    </row>
+    <row r="21" spans="6:10" ht="15.75" customHeight="1">
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
+      <c r="I21" s="5"/>
+      <c r="J21" s="5"/>
+    </row>
+    <row r="22" spans="6:10" ht="15.75" customHeight="1">
+      <c r="F22" s="5"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5"/>
+      <c r="I22" s="5"/>
+      <c r="J22" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -5903,439 +7098,459 @@
     <mergeCell ref="A10:D10"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink r:id="rId1" ref="F8"/>
-    <hyperlink r:id="rId2" ref="F9"/>
+    <hyperlink ref="F8" r:id="rId1" xr:uid="{00000000-0004-0000-0600-000000000000}"/>
+    <hyperlink ref="F9" r:id="rId2" xr:uid="{00000000-0004-0000-0600-000001000000}"/>
   </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:J23"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="23.13"/>
-    <col customWidth="1" min="4" max="4" width="33.13"/>
-    <col customWidth="1" min="6" max="6" width="46.0"/>
+    <col min="1" max="1" width="23.1640625" customWidth="1"/>
+    <col min="4" max="4" width="33.1640625" customWidth="1"/>
+    <col min="6" max="6" width="46" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="39" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="2">
+    <row r="1" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A1" s="57" t="s">
+        <v>53</v>
+      </c>
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+    </row>
+    <row r="2" spans="1:10" ht="15.75" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="40" t="s">
-        <v>59</v>
-      </c>
-      <c r="B3" s="40" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A3" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="B3" s="31" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="40" t="s">
+      <c r="C3" s="31" t="s">
         <v>18</v>
       </c>
       <c r="D3" s="1"/>
       <c r="F3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="G3" s="2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="35" t="s">
-        <v>61</v>
-      </c>
-      <c r="B4" s="35">
-        <v>70016.0</v>
-      </c>
-      <c r="C4" s="35">
-        <v>54895.0</v>
+      <c r="G3" s="2"/>
+    </row>
+    <row r="4" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A4" s="28" t="s">
+        <v>56</v>
+      </c>
+      <c r="B4" s="28">
+        <v>70016</v>
+      </c>
+      <c r="C4" s="28">
+        <v>54895</v>
       </c>
       <c r="D4" s="2"/>
       <c r="F4" s="3" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="35" t="s">
-        <v>63</v>
-      </c>
-      <c r="B5" s="35">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A5" s="28" t="s">
+        <v>58</v>
+      </c>
+      <c r="B5" s="28">
         <v>79.7</v>
       </c>
-      <c r="C5" s="35">
-        <v>78.0</v>
+      <c r="C5" s="28">
+        <v>78</v>
       </c>
       <c r="D5" s="2"/>
       <c r="F5" s="3" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="35" t="s">
-        <v>65</v>
-      </c>
-      <c r="B6" s="35">
-        <v>87887.0</v>
-      </c>
-      <c r="C6" s="35">
-        <v>70378.0</v>
+        <v>59</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A6" s="28" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" s="28">
+        <v>87887</v>
+      </c>
+      <c r="C6" s="28">
+        <v>70378</v>
       </c>
       <c r="D6" s="2"/>
     </row>
-    <row r="7">
-      <c r="A7" s="35" t="s">
-        <v>66</v>
-      </c>
-      <c r="B7" s="35">
-        <v>17871.0</v>
-      </c>
-      <c r="C7" s="35">
-        <v>15483.0</v>
+    <row r="7" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A7" s="28" t="s">
+        <v>61</v>
+      </c>
+      <c r="B7" s="28">
+        <v>17871</v>
+      </c>
+      <c r="C7" s="28">
+        <v>15483</v>
       </c>
       <c r="D7" s="2"/>
     </row>
-    <row r="8">
-      <c r="A8" s="16"/>
-      <c r="B8" s="41"/>
-      <c r="C8" s="41"/>
-      <c r="D8" s="42"/>
+    <row r="8" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A8" s="10"/>
+      <c r="B8" s="32"/>
+      <c r="C8" s="32"/>
+      <c r="D8" s="33"/>
       <c r="F8" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:10" ht="15.75" customHeight="1">
       <c r="A9" s="2"/>
-      <c r="B9" s="43"/>
-      <c r="C9" s="43"/>
-      <c r="D9" s="43"/>
+      <c r="B9" s="34"/>
+      <c r="C9" s="34"/>
+      <c r="D9" s="34"/>
       <c r="F9" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="G9" s="8"/>
-      <c r="H9" s="8"/>
-      <c r="I9" s="8"/>
-    </row>
-    <row r="10">
+        <v>62</v>
+      </c>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+    </row>
+    <row r="10" spans="1:10" ht="15.75" customHeight="1">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
     </row>
-    <row r="11">
-      <c r="A11" s="8"/>
+    <row r="11" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A11" s="50"/>
+      <c r="B11" s="48"/>
+      <c r="C11" s="48"/>
+      <c r="D11" s="48"/>
       <c r="F11" s="2" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="F12" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="15.75" customHeight="1">
+      <c r="F12" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="13">
-      <c r="F13" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6"/>
-      <c r="I13" s="6"/>
-      <c r="J13" s="6"/>
-    </row>
-    <row r="14">
-      <c r="D14" s="16" t="s">
-        <v>70</v>
-      </c>
-      <c r="F14" s="6"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
-      <c r="I14" s="6"/>
-      <c r="J14" s="6"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="16"/>
-      <c r="D15" s="16"/>
-      <c r="F15" s="6"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="6"/>
-      <c r="I15" s="6"/>
-      <c r="J15" s="6"/>
-    </row>
-    <row r="16">
-      <c r="F16" s="6"/>
-      <c r="G16" s="6"/>
-      <c r="H16" s="6"/>
-      <c r="I16" s="6"/>
-      <c r="J16" s="6"/>
-    </row>
-    <row r="17">
-      <c r="F17" s="6"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="6"/>
-      <c r="I17" s="6"/>
-      <c r="J17" s="6"/>
-    </row>
-    <row r="18">
-      <c r="D18" s="16"/>
-      <c r="F18" s="6"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="6"/>
-      <c r="I18" s="6"/>
-      <c r="J18" s="6"/>
-    </row>
-    <row r="19">
-      <c r="F19" s="6"/>
-      <c r="G19" s="6"/>
-      <c r="H19" s="6"/>
-      <c r="I19" s="6"/>
-      <c r="J19" s="6"/>
-    </row>
-    <row r="20">
-      <c r="F20" s="6"/>
-      <c r="G20" s="6"/>
-      <c r="H20" s="6"/>
-      <c r="I20" s="6"/>
-      <c r="J20" s="6"/>
-    </row>
-    <row r="21">
-      <c r="F21" s="6"/>
-      <c r="G21" s="6"/>
-      <c r="H21" s="6"/>
-      <c r="I21" s="6"/>
-      <c r="J21" s="6"/>
-    </row>
-    <row r="22">
-      <c r="F22" s="6"/>
-      <c r="G22" s="6"/>
-      <c r="H22" s="6"/>
-      <c r="I22" s="6"/>
-      <c r="J22" s="6"/>
-    </row>
-    <row r="23">
-      <c r="F23" s="6"/>
-      <c r="G23" s="6"/>
-      <c r="H23" s="6"/>
-      <c r="I23" s="6"/>
-      <c r="J23" s="6"/>
+    <row r="13" spans="1:10" ht="15.75" customHeight="1">
+      <c r="F13" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="5"/>
+    </row>
+    <row r="14" spans="1:10" ht="15.75" customHeight="1">
+      <c r="D14" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="5"/>
+    </row>
+    <row r="15" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A15" s="10"/>
+      <c r="D15" s="10"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="5"/>
+    </row>
+    <row r="16" spans="1:10" ht="15.75" customHeight="1">
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="5"/>
+    </row>
+    <row r="17" spans="4:10" ht="15.75" customHeight="1">
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="5"/>
+      <c r="J17" s="5"/>
+    </row>
+    <row r="18" spans="4:10" ht="15.75" customHeight="1">
+      <c r="D18" s="10"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
+      <c r="J18" s="5"/>
+    </row>
+    <row r="19" spans="4:10" ht="15.75" customHeight="1">
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="5"/>
+      <c r="J19" s="5"/>
+    </row>
+    <row r="20" spans="4:10" ht="15.75" customHeight="1">
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="5"/>
+      <c r="J20" s="5"/>
+    </row>
+    <row r="21" spans="4:10" ht="15.75" customHeight="1">
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
+      <c r="I21" s="5"/>
+      <c r="J21" s="5"/>
+    </row>
+    <row r="22" spans="4:10" ht="15.75" customHeight="1">
+      <c r="F22" s="5"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5"/>
+      <c r="I22" s="5"/>
+      <c r="J22" s="5"/>
+    </row>
+    <row r="23" spans="4:10" ht="15.75" customHeight="1">
+      <c r="F23" s="5"/>
+      <c r="G23" s="5"/>
+      <c r="H23" s="5"/>
+      <c r="I23" s="5"/>
+      <c r="J23" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A11:D11"/>
   </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:J23"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="26.5"/>
-    <col customWidth="1" min="4" max="4" width="33.13"/>
-    <col customWidth="1" min="5" max="5" width="15.5"/>
-    <col customWidth="1" min="6" max="6" width="62.13"/>
-    <col customWidth="1" min="7" max="7" width="36.0"/>
+    <col min="1" max="1" width="26.5" customWidth="1"/>
+    <col min="4" max="4" width="33.1640625" customWidth="1"/>
+    <col min="5" max="5" width="15.5" customWidth="1"/>
+    <col min="6" max="6" width="62.1640625" customWidth="1"/>
+    <col min="7" max="7" width="36" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="2">
+    <row r="1" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A1" s="47" t="s">
+        <v>66</v>
+      </c>
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+    </row>
+    <row r="2" spans="1:10" ht="15.75" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="34" t="s">
-        <v>59</v>
-      </c>
-      <c r="B3" s="34" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A3" s="27" t="s">
+        <v>55</v>
+      </c>
+      <c r="B3" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="34" t="s">
+      <c r="C3" s="27" t="s">
         <v>18</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="G3" s="6" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="35" t="s">
-        <v>74</v>
-      </c>
-      <c r="B4" s="36">
-        <v>87887.0</v>
-      </c>
-      <c r="C4" s="36">
-        <v>70378.0</v>
+      <c r="G3" s="5" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A4" s="28" t="s">
+        <v>69</v>
+      </c>
+      <c r="B4" s="29">
+        <v>87887</v>
+      </c>
+      <c r="C4" s="29">
+        <v>70378</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="35" t="s">
+    <row r="5" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A5" s="28" t="s">
+        <v>70</v>
+      </c>
+      <c r="B5" s="29">
+        <v>27026243</v>
+      </c>
+      <c r="C5" s="29">
+        <v>32897563</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A6" s="28" t="s">
+        <v>72</v>
+      </c>
+      <c r="B6" s="29">
+        <v>6610302</v>
+      </c>
+      <c r="C6" s="29">
+        <v>18736254</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A7" s="35" t="s">
+        <v>73</v>
+      </c>
+      <c r="B7" s="36">
+        <v>308</v>
+      </c>
+      <c r="C7" s="36">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A8" s="37"/>
+      <c r="B8" s="38"/>
+      <c r="C8" s="38"/>
+      <c r="F8" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="G8" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="B5" s="36">
-        <v>2.7026243E7</v>
-      </c>
-      <c r="C5" s="36">
-        <v>3.2897563E7</v>
-      </c>
-      <c r="F5" s="3" t="s">
+    </row>
+    <row r="9" spans="1:10" ht="15.75" customHeight="1">
+      <c r="F9" s="50"/>
+      <c r="G9" s="48"/>
+      <c r="H9" s="48"/>
+      <c r="I9" s="48"/>
+    </row>
+    <row r="10" spans="1:10" ht="15.75" customHeight="1">
+      <c r="F10" s="4" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="35" t="s">
+    <row r="11" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A11" s="50"/>
+      <c r="B11" s="48"/>
+      <c r="C11" s="48"/>
+      <c r="D11" s="48"/>
+      <c r="F11" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="B6" s="36">
-        <v>6610302.0</v>
-      </c>
-      <c r="C6" s="36">
-        <v>1.8736254E7</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="44" t="s">
+    </row>
+    <row r="12" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A12" s="55" t="s">
         <v>78</v>
       </c>
-      <c r="B7" s="45">
-        <v>308.0</v>
-      </c>
-      <c r="C7" s="45">
-        <v>467.0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="46"/>
-      <c r="B8" s="47"/>
-      <c r="C8" s="47"/>
-      <c r="F8" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="F9" s="8"/>
-    </row>
-    <row r="10">
-      <c r="F10" s="5" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="8"/>
-      <c r="F11" s="6" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
-    </row>
-    <row r="13">
-      <c r="F13" s="6"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6"/>
-      <c r="I13" s="6"/>
-      <c r="J13" s="6"/>
-    </row>
-    <row r="14">
-      <c r="F14" s="6"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
-      <c r="I14" s="6"/>
-      <c r="J14" s="6"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="6"/>
-      <c r="F15" s="6"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="6"/>
-      <c r="I15" s="6"/>
-      <c r="J15" s="6"/>
-    </row>
-    <row r="16">
-      <c r="F16" s="6"/>
-      <c r="G16" s="6"/>
-      <c r="H16" s="6"/>
-      <c r="I16" s="6"/>
-      <c r="J16" s="6"/>
-    </row>
-    <row r="17">
-      <c r="F17" s="6"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="6"/>
-      <c r="I17" s="6"/>
-      <c r="J17" s="6"/>
-    </row>
-    <row r="18">
-      <c r="F18" s="6"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="6"/>
-      <c r="I18" s="6"/>
-      <c r="J18" s="6"/>
-    </row>
-    <row r="19">
-      <c r="F19" s="6"/>
-      <c r="G19" s="6"/>
-      <c r="H19" s="6"/>
-      <c r="I19" s="6"/>
-      <c r="J19" s="6"/>
-    </row>
-    <row r="20">
-      <c r="F20" s="6"/>
-      <c r="G20" s="6"/>
-      <c r="H20" s="6"/>
-      <c r="I20" s="6"/>
-      <c r="J20" s="6"/>
-    </row>
-    <row r="21">
-      <c r="F21" s="6"/>
-      <c r="G21" s="6"/>
-      <c r="H21" s="6"/>
-      <c r="I21" s="6"/>
-      <c r="J21" s="6"/>
-    </row>
-    <row r="22">
-      <c r="F22" s="6"/>
-      <c r="G22" s="6"/>
-      <c r="H22" s="6"/>
-      <c r="I22" s="6"/>
-      <c r="J22" s="6"/>
-    </row>
-    <row r="23">
-      <c r="F23" s="6"/>
-      <c r="G23" s="6"/>
-      <c r="H23" s="6"/>
-      <c r="I23" s="6"/>
-      <c r="J23" s="6"/>
+      <c r="B12" s="48"/>
+      <c r="C12" s="48"/>
+      <c r="D12" s="48"/>
+      <c r="F12" s="4"/>
+      <c r="G12" s="4"/>
+    </row>
+    <row r="13" spans="1:10" ht="15.75" customHeight="1">
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="5"/>
+    </row>
+    <row r="14" spans="1:10" ht="15.75" customHeight="1">
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="5"/>
+    </row>
+    <row r="15" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="5"/>
+    </row>
+    <row r="16" spans="1:10" ht="15.75" customHeight="1">
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="5"/>
+    </row>
+    <row r="17" spans="6:10" ht="15.75" customHeight="1">
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="5"/>
+      <c r="J17" s="5"/>
+    </row>
+    <row r="18" spans="6:10" ht="15.75" customHeight="1">
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
+      <c r="J18" s="5"/>
+    </row>
+    <row r="19" spans="6:10" ht="15.75" customHeight="1">
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="5"/>
+      <c r="J19" s="5"/>
+    </row>
+    <row r="20" spans="6:10" ht="15.75" customHeight="1">
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="5"/>
+      <c r="J20" s="5"/>
+    </row>
+    <row r="21" spans="6:10" ht="15.75" customHeight="1">
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
+      <c r="I21" s="5"/>
+      <c r="J21" s="5"/>
+    </row>
+    <row r="22" spans="6:10" ht="15.75" customHeight="1">
+      <c r="F22" s="5"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5"/>
+      <c r="I22" s="5"/>
+      <c r="J22" s="5"/>
+    </row>
+    <row r="23" spans="6:10" ht="15.75" customHeight="1">
+      <c r="F23" s="5"/>
+      <c r="G23" s="5"/>
+      <c r="H23" s="5"/>
+      <c r="I23" s="5"/>
+      <c r="J23" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -6344,6 +7559,7 @@
     <mergeCell ref="A11:D11"/>
     <mergeCell ref="A12:D12"/>
   </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>